--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_01/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_01/pre_sizing_results_optimized.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,67 +429,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -485,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>149.9999995291259</v>
+        <v>149.9739746349477</v>
       </c>
       <c r="B2" t="n">
-        <v>46.63843862145523</v>
+        <v>178.3029836677493</v>
       </c>
       <c r="C2" t="n">
-        <v>33.67037955174705</v>
+        <v>33.43172107109731</v>
       </c>
       <c r="D2" t="n">
-        <v>17.46219033034069</v>
+        <v>16.49797198212473</v>
       </c>
       <c r="E2" t="n">
-        <v>4.72837221949559</v>
+        <v>4.559289230158716</v>
       </c>
       <c r="F2" t="n">
-        <v>12.63953578858603</v>
+        <v>12.52859170762953</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007277207435159788</v>
+        <v>0.0007723109268011157</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.981447876771512</v>
+        <v>-0.9836491948031302</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.035893539507863</v>
+        <v>-1.026097403839717</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9988889218385888</v>
+        <v>-0.9988881504189049</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.004881973291302046</v>
+        <v>-0.001953455568895634</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2440139412981219</v>
+        <v>-0.2437547309324885</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08112903514540704</v>
+        <v>-0.040962848168525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>37.21882993171977</v>
+        <v>35.4955685957508</v>
       </c>
       <c r="B3" t="n">
-        <v>52.1177332508964</v>
+        <v>42.22838215294913</v>
       </c>
       <c r="C3" t="n">
-        <v>5.013857704259754</v>
+        <v>5.031204631355706</v>
       </c>
       <c r="D3" t="n">
-        <v>5.000463504373037</v>
+        <v>5.007910403956627</v>
       </c>
       <c r="E3" t="n">
-        <v>4.985455915244136</v>
+        <v>4.955969419274921</v>
       </c>
       <c r="F3" t="n">
-        <v>2.279880980712556</v>
+        <v>2.144166590095645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1037364359827689</v>
+        <v>0.1396094339258905</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02325666075653727</v>
+        <v>-0.0009192572442519817</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4329760439172682</v>
+        <v>-0.4547393137950965</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7068710051409154</v>
+        <v>-0.6456657832987837</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.01789544119788931</v>
+        <v>-0.008750874280016472</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.523920238435242</v>
+        <v>-0.5396282688555419</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01928115053221355</v>
+        <v>-0.02073317149748199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>37.21882993171977</v>
+        <v>112.5449116697022</v>
       </c>
       <c r="B4" t="n">
-        <v>52.29714867560677</v>
+        <v>42.35583705636097</v>
       </c>
       <c r="C4" t="n">
-        <v>5.013857704259754</v>
+        <v>25.02599837454213</v>
       </c>
       <c r="D4" t="n">
-        <v>5.000463504373037</v>
+        <v>7.295584240006981</v>
       </c>
       <c r="E4" t="n">
-        <v>4.98570417134167</v>
+        <v>4.998770577663387</v>
       </c>
       <c r="F4" t="n">
-        <v>2.279880980712556</v>
+        <v>9.767826869716426</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1037364359827689</v>
+        <v>0.001892147443752845</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02325666075653727</v>
+        <v>-0.9650949591360375</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4329760439172682</v>
+        <v>-1.030492877125445</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7068710051409154</v>
+        <v>-0.9964940462419679</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.01789544119788931</v>
+        <v>-0.241792919033967</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.523920238435242</v>
+        <v>-0.7097165106259004</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01928115053221355</v>
+        <v>-0.2201715279536512</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>46.47471105303412</v>
+        <v>120.8923679106476</v>
       </c>
       <c r="B5" t="n">
-        <v>48.0731141857606</v>
+        <v>47.02350972416204</v>
       </c>
       <c r="C5" t="n">
-        <v>33.55615374551437</v>
+        <v>5.014229535118981</v>
       </c>
       <c r="D5" t="n">
-        <v>5.076958893241468</v>
+        <v>5.006943496194459</v>
       </c>
       <c r="E5" t="n">
-        <v>4.700707036574954</v>
+        <v>4.995682652423563</v>
       </c>
       <c r="F5" t="n">
-        <v>3.156597295605176</v>
+        <v>10.6023311470982</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04410192765935363</v>
+        <v>0.001472872129219644</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4935111014829153</v>
+        <v>-0.9714505128331454</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7040093519828488</v>
+        <v>-1.03587766471941</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.879429003863659</v>
+        <v>-0.9973666165271042</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0004922780108521633</v>
+        <v>-0.9608326542123716</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7100280017413474</v>
+        <v>-0.4793628735685255</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06115273540896698</v>
+        <v>-0.01709724096387663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53.98345207488772</v>
+        <v>141.5942569203485</v>
       </c>
       <c r="B6" t="n">
-        <v>53.70258518246914</v>
+        <v>47.81003047864017</v>
       </c>
       <c r="C6" t="n">
-        <v>5.000656166494776</v>
+        <v>40.42603035751971</v>
       </c>
       <c r="D6" t="n">
-        <v>5.000391456113594</v>
+        <v>16.35777178757917</v>
       </c>
       <c r="E6" t="n">
-        <v>4.973304943794354</v>
+        <v>4.97605134645621</v>
       </c>
       <c r="F6" t="n">
-        <v>3.755591949464827</v>
+        <v>11.45938943186948</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0246895646812857</v>
+        <v>0.0009380277247078556</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6750127572556319</v>
+        <v>-0.9808693269549533</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8217275799401633</v>
+        <v>-1.022707930578448</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9337681279397945</v>
+        <v>-0.9986006476303895</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.646217520931474</v>
+        <v>-0.02685924496605617</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5096658263205281</v>
+        <v>-0.1602919634054581</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0232015262324351</v>
+        <v>-0.05742202726027779</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43.86949178343581</v>
+        <v>44.29013755299038</v>
       </c>
       <c r="B7" t="n">
-        <v>46.69604169669591</v>
+        <v>41.24626267982941</v>
       </c>
       <c r="C7" t="n">
-        <v>5.002726222833591</v>
+        <v>5.068863138628119</v>
       </c>
       <c r="D7" t="n">
-        <v>5.000531813008739</v>
+        <v>5.000362355193743</v>
       </c>
       <c r="E7" t="n">
-        <v>4.971487344777413</v>
+        <v>4.601217897260672</v>
       </c>
       <c r="F7" t="n">
-        <v>2.892202724265689</v>
+        <v>3.111165074865225</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05473291102280176</v>
+        <v>0.05877557927583388</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4003966320111453</v>
+        <v>-0.4824781923194221</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6472721914742215</v>
+        <v>-0.7205202113727757</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8481344633109273</v>
+        <v>-0.8538221648214264</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4384011781895923</v>
+        <v>-4.72943673477331</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4190217065655198</v>
+        <v>-0.2354644486960626</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02362723643912827</v>
+        <v>-0.07165449340713684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>42.07079527919285</v>
+        <v>40.91902383016981</v>
       </c>
       <c r="B8" t="n">
-        <v>44.54209674281571</v>
+        <v>42.28813155864844</v>
       </c>
       <c r="C8" t="n">
-        <v>5.013788367853858</v>
+        <v>5.00539049121349</v>
       </c>
       <c r="D8" t="n">
-        <v>5.000463466984842</v>
+        <v>5.007892589997413</v>
       </c>
       <c r="E8" t="n">
-        <v>4.971210008792776</v>
+        <v>4.995375358487403</v>
       </c>
       <c r="F8" t="n">
-        <v>2.831584680836036</v>
+        <v>2.696982375374803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06431317818743523</v>
+        <v>0.0800078525737411</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3213713182258103</v>
+        <v>-0.3454275163399115</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6004016719668661</v>
+        <v>-0.6405333791105748</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8204494435559658</v>
+        <v>-0.7993641279354686</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.824036520710501</v>
+        <v>-2.853988765799904</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3238838702420463</v>
+        <v>-0.3697708731068811</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02152702589531579</v>
+        <v>-0.01753966466438424</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>41.35271659128303</v>
+        <v>36.14597030995213</v>
       </c>
       <c r="B9" t="n">
-        <v>48.92952560087375</v>
+        <v>42.15279421406962</v>
       </c>
       <c r="C9" t="n">
-        <v>5.079322895516676</v>
+        <v>5.012333225105918</v>
       </c>
       <c r="D9" t="n">
-        <v>5.002405138000835</v>
+        <v>5.002875604561468</v>
       </c>
       <c r="E9" t="n">
-        <v>4.645718096992431</v>
+        <v>4.999028376935183</v>
       </c>
       <c r="F9" t="n">
-        <v>2.673920925133842</v>
+        <v>2.189942689251313</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06883002480733991</v>
+        <v>0.1300232502351399</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.28560055633394</v>
+        <v>-0.05345319590585201</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5795158151783141</v>
+        <v>-0.481564233937695</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8076494368167458</v>
+        <v>-0.6704888672290567</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4877794074870393</v>
+        <v>-0.03775173058093424</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4312744575029391</v>
+        <v>-0.5445465559250192</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06957723910490207</v>
+        <v>-0.01670720468597553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>57.26729175935255</v>
+        <v>147.3152891623997</v>
       </c>
       <c r="B10" t="n">
-        <v>84.43140221303452</v>
+        <v>44.00350900009624</v>
       </c>
       <c r="C10" t="n">
-        <v>39.91141607608049</v>
+        <v>39.68665995889379</v>
       </c>
       <c r="D10" t="n">
-        <v>8.379066955623351</v>
+        <v>16.62596275560317</v>
       </c>
       <c r="E10" t="n">
-        <v>4.982469165418014</v>
+        <v>4.031812984859531</v>
       </c>
       <c r="F10" t="n">
-        <v>4.120552731333725</v>
+        <v>12.22800030613252</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02016584184324535</v>
+        <v>0.0008211466213306919</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7249982741866728</v>
+        <v>-0.9828249900965085</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8552649767272349</v>
+        <v>-1.025076322366162</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9477022431999064</v>
+        <v>-0.9988056864709159</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.008425142353455458</v>
+        <v>-0.1297792526049207</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6302583668330689</v>
+        <v>-0.2172739764392707</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09044800672883466</v>
+        <v>-0.08791135833983225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>44.20333743166065</v>
+        <v>43.7226087998168</v>
       </c>
       <c r="B11" t="n">
-        <v>37.35809581932652</v>
+        <v>47.08202892440812</v>
       </c>
       <c r="C11" t="n">
-        <v>5.082747949949466</v>
+        <v>5.01420094578129</v>
       </c>
       <c r="D11" t="n">
-        <v>5.000025889859114</v>
+        <v>5.00047978100545</v>
       </c>
       <c r="E11" t="n">
-        <v>4.949273617024763</v>
+        <v>4.985870440955138</v>
       </c>
       <c r="F11" t="n">
-        <v>3.092635240633177</v>
+        <v>2.874848061794461</v>
       </c>
       <c r="G11" t="n">
-        <v>0.05308186741709243</v>
+        <v>0.06186243920709186</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4139361779058677</v>
+        <v>-0.4621257722671988</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6554879818752449</v>
+        <v>-0.7057259550830897</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8526706069025326</v>
+        <v>-0.8460834310266007</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.130001305556676</v>
+        <v>-0.4046699876681268</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2389225978101979</v>
+        <v>-0.4225712634096477</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02470048160498004</v>
+        <v>-0.0193517464007409</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39.56187288033114</v>
+        <v>36.501954691339</v>
       </c>
       <c r="B12" t="n">
-        <v>47.42063749430962</v>
+        <v>42.22838215294913</v>
       </c>
       <c r="C12" t="n">
-        <v>5.05292245604434</v>
+        <v>5.080597971742067</v>
       </c>
       <c r="D12" t="n">
-        <v>5.014798040871954</v>
+        <v>5.007735027073608</v>
       </c>
       <c r="E12" t="n">
-        <v>4.831940506207071</v>
+        <v>4.999765676634778</v>
       </c>
       <c r="F12" t="n">
-        <v>2.550508340607615</v>
+        <v>2.229232773004596</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0817217877028599</v>
+        <v>0.1251213758892871</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1854010611164279</v>
+        <v>-0.08065911252570607</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5223303587885738</v>
+        <v>-0.4958601389555355</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7703839351938345</v>
+        <v>-0.6831562421434965</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.205186446306454</v>
+        <v>-0.3300952698237499</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4238402716634129</v>
+        <v>-0.5303766327908134</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04481639259846663</v>
+        <v>-0.01747862059549976</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>38.48420514956575</v>
+        <v>49.02104011961399</v>
       </c>
       <c r="B13" t="n">
-        <v>48.3099446118938</v>
+        <v>46.36734011310568</v>
       </c>
       <c r="C13" t="n">
-        <v>5.31961227783523</v>
+        <v>34.80348362031872</v>
       </c>
       <c r="D13" t="n">
-        <v>5.02846844996923</v>
+        <v>5.00001540943815</v>
       </c>
       <c r="E13" t="n">
-        <v>4.972493846170532</v>
+        <v>4.404141928864912</v>
       </c>
       <c r="F13" t="n">
-        <v>2.439791310779903</v>
+        <v>3.436084714834831</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09103450666471959</v>
+        <v>0.03996174807821577</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1156821914828036</v>
+        <v>-0.6158980331545129</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4834480293107136</v>
+        <v>-0.7955398115985961</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7435636670257415</v>
+        <v>-0.902595380297361</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.466728499700136</v>
+        <v>-0.3655785393054464</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4667749548342079</v>
+        <v>-0.7015021770716098</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03001743775180682</v>
+        <v>-0.1377062285971517</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73.89225709816638</v>
+        <v>98.96873712093605</v>
       </c>
       <c r="B14" t="n">
-        <v>47.09747491168772</v>
+        <v>54.45132601993453</v>
       </c>
       <c r="C14" t="n">
-        <v>40.69059472805147</v>
+        <v>30.03868169361854</v>
       </c>
       <c r="D14" t="n">
-        <v>6.719373931623223</v>
+        <v>9.724614969443204</v>
       </c>
       <c r="E14" t="n">
-        <v>3.081261684005552</v>
+        <v>4.449647424415007</v>
       </c>
       <c r="F14" t="n">
-        <v>5.964464064772488</v>
+        <v>8.0545804803096</v>
       </c>
       <c r="G14" t="n">
-        <v>0.007696708566176536</v>
+        <v>0.002988200005704127</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8697305456561654</v>
+        <v>-0.9497498100177056</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9601336656551049</v>
+        <v>-1.017183129040092</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9811325194171358</v>
+        <v>-0.9941370319420683</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6404427861276846</v>
+        <v>-0.03554332641820265</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.693695940073204</v>
+        <v>-0.6143033673775294</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.004084862322197577</v>
+        <v>-0.1713201224830808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104.6938581650893</v>
+        <v>42.18758861530865</v>
       </c>
       <c r="B15" t="n">
-        <v>43.83457765321673</v>
+        <v>48.06694643226223</v>
       </c>
       <c r="C15" t="n">
-        <v>29.70794024946924</v>
+        <v>5.014229535118981</v>
       </c>
       <c r="D15" t="n">
-        <v>8.90062164907952</v>
+        <v>5.002410236723948</v>
       </c>
       <c r="E15" t="n">
-        <v>4.650245770774648</v>
+        <v>4.98634010164084</v>
       </c>
       <c r="F15" t="n">
-        <v>8.768293029739754</v>
+        <v>2.729064619506631</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002247886547360123</v>
+        <v>0.07108695633897659</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.951637872922155</v>
+        <v>-0.4019901528694835</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.020667873062074</v>
+        <v>-0.670837885634221</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9953180709987038</v>
+        <v>-0.8224294938573756</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.03898255779535251</v>
+        <v>-0.2077666157445091</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.657070420789703</v>
+        <v>-0.4326494074248414</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1497366942187777</v>
+        <v>-0.01935762648516606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40.50346922955199</v>
+        <v>39.79996870768129</v>
       </c>
       <c r="B16" t="n">
-        <v>48.28308274294484</v>
+        <v>50.32270070411327</v>
       </c>
       <c r="C16" t="n">
-        <v>5.05292245604434</v>
+        <v>5.005340356681886</v>
       </c>
       <c r="D16" t="n">
-        <v>5.014798040871954</v>
+        <v>5.001665066104809</v>
       </c>
       <c r="E16" t="n">
-        <v>4.831940506207071</v>
+        <v>4.993520508782826</v>
       </c>
       <c r="F16" t="n">
-        <v>2.64276726706658</v>
+        <v>2.505166878646001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07457037782067645</v>
+        <v>0.08921474898732269</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.240353299495843</v>
+        <v>-0.2890829056097003</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5534993360525982</v>
+        <v>-0.6072209443576277</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7910026646033358</v>
+        <v>-0.775829366152355</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.309855457982176</v>
+        <v>-0.01425815962850511</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3982495863292389</v>
+        <v>-0.4666088913417988</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.04481639259846663</v>
+        <v>-0.01752935329300378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47.43030374130119</v>
+        <v>46.34978620387996</v>
       </c>
       <c r="B17" t="n">
-        <v>52.16179192193534</v>
+        <v>62.22907968223483</v>
       </c>
       <c r="C17" t="n">
-        <v>33.3790555865916</v>
+        <v>33.44176097280643</v>
       </c>
       <c r="D17" t="n">
-        <v>5.001772589170218</v>
+        <v>5.000052085293337</v>
       </c>
       <c r="E17" t="n">
-        <v>4.65056199253443</v>
+        <v>4.997602087486567</v>
       </c>
       <c r="F17" t="n">
-        <v>3.238405650471257</v>
+        <v>3.118492937457514</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04076683595206091</v>
+        <v>0.04964430791746174</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5231243223878971</v>
+        <v>-0.5466128246300566</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7225686730105159</v>
+        <v>-0.7517073951724401</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8888560009970286</v>
+        <v>-0.8781238571025956</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.02922358075879809</v>
+        <v>-0.001206040220972539</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7277258471955982</v>
+        <v>-0.7259932444180214</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0329598574944255</v>
+        <v>-0.04263100105412412</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80.34055392277217</v>
+        <v>39.09575539385997</v>
       </c>
       <c r="B18" t="n">
-        <v>36.52607219288208</v>
+        <v>48.11755393988712</v>
       </c>
       <c r="C18" t="n">
-        <v>5.37244568788226</v>
+        <v>5.014229535118981</v>
       </c>
       <c r="D18" t="n">
-        <v>5.029766937084531</v>
+        <v>5.007252338673442</v>
       </c>
       <c r="E18" t="n">
-        <v>4.963911500110962</v>
+        <v>4.985651622063745</v>
       </c>
       <c r="F18" t="n">
-        <v>6.400108120470859</v>
+        <v>2.492819801593517</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005623962368824413</v>
+        <v>0.09561394257488336</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8979698520880753</v>
+        <v>-0.2504692441266388</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9815841515635636</v>
+        <v>-0.5872579933650973</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9864988626538466</v>
+        <v>-0.7592361901715431</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.734968484588317</v>
+        <v>-1.815218049418966</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4435582818065676</v>
+        <v>-0.4424105656702617</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.01976767436731055</v>
+        <v>-0.01935762648516606</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>63.44278424411045</v>
+        <v>82.83566337736643</v>
       </c>
       <c r="B19" t="n">
-        <v>38.24994789547299</v>
+        <v>47.24130081265413</v>
       </c>
       <c r="C19" t="n">
-        <v>5.77561042171504</v>
+        <v>5.011481586109512</v>
       </c>
       <c r="D19" t="n">
-        <v>5.076958893241468</v>
+        <v>5.000166872265702</v>
       </c>
       <c r="E19" t="n">
-        <v>4.679665808278139</v>
+        <v>4.984683219168414</v>
       </c>
       <c r="F19" t="n">
-        <v>5.058753895757167</v>
+        <v>6.766745023532606</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01339810730509903</v>
+        <v>0.005530587057501649</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7976908488661125</v>
+        <v>-0.9171640130319869</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9073732947201072</v>
+        <v>-1.001432915340734</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9652799209168055</v>
+        <v>-0.9880535127497827</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.557109373848001</v>
+        <v>-3.38225479577378</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1402452588055171</v>
+        <v>-0.3331070722678858</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.06894911181497528</v>
+        <v>-0.01879244472590753</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120.763806492501</v>
+        <v>108.7512570909628</v>
       </c>
       <c r="B20" t="n">
-        <v>48.52701456246923</v>
+        <v>42.47728524265948</v>
       </c>
       <c r="C20" t="n">
-        <v>5.049641900794514</v>
+        <v>34.03285995804202</v>
       </c>
       <c r="D20" t="n">
-        <v>5.09855364476676</v>
+        <v>7.208047338815298</v>
       </c>
       <c r="E20" t="n">
-        <v>4.688915715929169</v>
+        <v>4.922266148034682</v>
       </c>
       <c r="F20" t="n">
-        <v>10.59632548096512</v>
+        <v>9.180755905265233</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001368206086145731</v>
+        <v>0.00213170119299671</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9676279428840279</v>
+        <v>-0.9615734153240343</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.031132596874486</v>
+        <v>-1.027493726855034</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9973553849329815</v>
+        <v>-0.9959786442103421</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.840462226140932</v>
+        <v>-0.1552576990947117</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4855305995672722</v>
+        <v>-0.6873794736881632</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06347631830723849</v>
+        <v>-0.127803370075858</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>70.09087705133796</v>
+        <v>136.9492101778452</v>
       </c>
       <c r="B21" t="n">
-        <v>47.09747491168772</v>
+        <v>36.10901482333475</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09537782787817</v>
+        <v>40.42603035751971</v>
       </c>
       <c r="D21" t="n">
-        <v>6.756932580069303</v>
+        <v>17.68815524282077</v>
       </c>
       <c r="E21" t="n">
-        <v>4.735681173790134</v>
+        <v>3.51982777939361</v>
       </c>
       <c r="F21" t="n">
-        <v>5.448685813492512</v>
+        <v>11.02339181973048</v>
       </c>
       <c r="G21" t="n">
-        <v>0.009364362562991025</v>
+        <v>0.001056101417376682</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8480897671220647</v>
+        <v>-0.9789902648368467</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9439469112985477</v>
+        <v>-1.020380828604205</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9766942188058599</v>
+        <v>-0.99840091512824</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3748604261558894</v>
+        <v>-0.1044280223605757</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7154077680054856</v>
+        <v>-0.1140268659850158</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08971540123373462</v>
+        <v>-0.05742202726027779</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115.5167522399323</v>
+        <v>103.1918498890741</v>
       </c>
       <c r="B22" t="n">
-        <v>44.88053706948293</v>
+        <v>33.59034204727364</v>
       </c>
       <c r="C22" t="n">
-        <v>31.6122663429769</v>
+        <v>33.25265484843973</v>
       </c>
       <c r="D22" t="n">
-        <v>5.003028489640609</v>
+        <v>8.449455701350852</v>
       </c>
       <c r="E22" t="n">
-        <v>3.122074914097151</v>
+        <v>3.940764017705823</v>
       </c>
       <c r="F22" t="n">
-        <v>9.983459654155494</v>
+        <v>8.50639193418945</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00159267221679374</v>
+        <v>0.002569160126865354</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9633611276837859</v>
+        <v>-0.9554084838397224</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.028540669313526</v>
+        <v>-1.022144044647802</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9968411444875692</v>
+        <v>-0.9950394703447246</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1009257176741876</v>
+        <v>-0.07249126346128057</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6707627348582784</v>
+        <v>-0.6458503142329221</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.09239691838175502</v>
+        <v>-0.01782944193183799</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40.1436206150483</v>
+        <v>77.18673594266508</v>
       </c>
       <c r="B23" t="n">
-        <v>48.79240467030234</v>
+        <v>105.1075451445388</v>
       </c>
       <c r="C23" t="n">
-        <v>5.079322895516676</v>
+        <v>33.75067277097235</v>
       </c>
       <c r="D23" t="n">
-        <v>5.000010328476892</v>
+        <v>13.69998754043308</v>
       </c>
       <c r="E23" t="n">
-        <v>4.953621197167415</v>
+        <v>4.381569945881886</v>
       </c>
       <c r="F23" t="n">
-        <v>2.598560377394456</v>
+        <v>5.843277265870609</v>
       </c>
       <c r="G23" t="n">
-        <v>0.07720533952145277</v>
+        <v>0.007511459797016021</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2199590745336565</v>
+        <v>-0.8967782850147993</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5418745683164619</v>
+        <v>-0.9711988419114191</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7834074652419186</v>
+        <v>-0.9841532962705758</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.07995748272421</v>
+        <v>-0.1283103726396377</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4120174329460549</v>
+        <v>-0.4515902997182021</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.02399593632020088</v>
+        <v>-0.0971522625273884</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110.0310305795524</v>
+        <v>40.27770817229933</v>
       </c>
       <c r="B24" t="n">
-        <v>50.08523125257215</v>
+        <v>47.38307340408939</v>
       </c>
       <c r="C24" t="n">
-        <v>35.37893028567608</v>
+        <v>5.000789608330932</v>
       </c>
       <c r="D24" t="n">
-        <v>6.734525459597517</v>
+        <v>5.008004795481336</v>
       </c>
       <c r="E24" t="n">
-        <v>2.865668039766523</v>
+        <v>4.915116038441898</v>
       </c>
       <c r="F24" t="n">
-        <v>9.336913707986259</v>
+        <v>2.626917421994017</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001885533672757102</v>
+        <v>0.08510391008257012</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9579963352300941</v>
+        <v>-0.3139660555600379</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.025051841440994</v>
+        <v>-0.6227023720942068</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9961624953080809</v>
+        <v>-0.7862773066957701</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.06683870276477291</v>
+        <v>-2.491664358902037</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6969394708864562</v>
+        <v>-0.3953211274172551</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.05131360684192424</v>
+        <v>-0.03606938632091818</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87.11930366915078</v>
+        <v>59.36812946597895</v>
       </c>
       <c r="B25" t="n">
-        <v>73.29941101707696</v>
+        <v>42.82518340456449</v>
       </c>
       <c r="C25" t="n">
-        <v>33.67529702554651</v>
+        <v>6.16921622481963</v>
       </c>
       <c r="D25" t="n">
-        <v>12.28348961162119</v>
+        <v>5.000259048792489</v>
       </c>
       <c r="E25" t="n">
-        <v>4.981505659637366</v>
+        <v>4.378152353060625</v>
       </c>
       <c r="F25" t="n">
-        <v>6.813130518652729</v>
+        <v>4.522348183725208</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004366561399283105</v>
+        <v>0.01909640278630994</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9180974431295574</v>
+        <v>-0.7818472776171824</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9958248310942232</v>
+        <v>-0.907363533140734</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9902354538985797</v>
+        <v>-0.9547210674718907</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05825097077991385</v>
+        <v>-3.477196835521541</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5257872732324055</v>
+        <v>-0.2861996286278347</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08211036086125088</v>
+        <v>-0.1200044004655384</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67.36901500304168</v>
+        <v>38.59332106173631</v>
       </c>
       <c r="B26" t="n">
-        <v>44.54096628131896</v>
+        <v>47.18871693531933</v>
       </c>
       <c r="C26" t="n">
-        <v>39.47639249881556</v>
+        <v>5.073745409549354</v>
       </c>
       <c r="D26" t="n">
-        <v>6.756932580069303</v>
+        <v>5.00028911716211</v>
       </c>
       <c r="E26" t="n">
-        <v>4.989690997049125</v>
+        <v>4.762893682042064</v>
       </c>
       <c r="F26" t="n">
-        <v>5.384181141512301</v>
+        <v>2.44514000965034</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01081675655187259</v>
+        <v>0.1005891314109025</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8296742857615956</v>
+        <v>-0.2210566978899748</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9303991888438773</v>
+        <v>-0.5710659620214111</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9726933230918441</v>
+        <v>-0.7464515075955748</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6178474589135914</v>
+        <v>-1.50614327434105</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5048055115085081</v>
+        <v>-0.4624277363138869</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.08055794042978094</v>
+        <v>-0.05149906138563906</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>38.06040754088804</v>
+        <v>93.07377152971874</v>
       </c>
       <c r="B27" t="n">
-        <v>47.45555221565668</v>
+        <v>50.17571405211805</v>
       </c>
       <c r="C27" t="n">
-        <v>5.034751955497219</v>
+        <v>33.71474961851718</v>
       </c>
       <c r="D27" t="n">
-        <v>5.000012425773832</v>
+        <v>9.576533273288181</v>
       </c>
       <c r="E27" t="n">
-        <v>4.704545023732952</v>
+        <v>4.997214681696943</v>
       </c>
       <c r="F27" t="n">
-        <v>2.388031028048043</v>
+        <v>7.614766039396407</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09505099189294351</v>
+        <v>0.003706902455663339</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.08610478971381168</v>
+        <v>-0.94023431170302</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.467171968664669</v>
+        <v>-1.011152586742817</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7319499422652319</v>
+        <v>-0.9925045037476395</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.196871702550099</v>
+        <v>-0.1719857961468982</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4836592091712982</v>
+        <v>-0.4682197875624573</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.06041569389789182</v>
+        <v>-0.08998347734701517</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52.01613256031546</v>
+        <v>42.48334619544718</v>
       </c>
       <c r="B28" t="n">
-        <v>37.35798056938457</v>
+        <v>47.01130151837435</v>
       </c>
       <c r="C28" t="n">
-        <v>5.030374521842911</v>
+        <v>5.00375898647579</v>
       </c>
       <c r="D28" t="n">
-        <v>5.013780147661057</v>
+        <v>5.006641807806374</v>
       </c>
       <c r="E28" t="n">
-        <v>4.898501309760111</v>
+        <v>4.993597738167178</v>
       </c>
       <c r="F28" t="n">
-        <v>3.593150691714338</v>
+        <v>2.82083295796784</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02844117628489414</v>
+        <v>0.06914506251205919</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.637479926024288</v>
+        <v>-0.4143494707896268</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7966240761694932</v>
+        <v>-0.6791660417354575</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9231652988287679</v>
+        <v>-0.8273228882238359</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4640360227069596</v>
+        <v>-2.09803114208366</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5023625757631793</v>
+        <v>-0.3672936690376655</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.03340097198465408</v>
+        <v>-0.01946336607942386</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>59.22339750646957</v>
+        <v>37.75089245544008</v>
       </c>
       <c r="B29" t="n">
-        <v>48.52701456246923</v>
+        <v>47.40144676512313</v>
       </c>
       <c r="C29" t="n">
-        <v>5.049641900794514</v>
+        <v>5.00047260669423</v>
       </c>
       <c r="D29" t="n">
-        <v>5.09855364476676</v>
+        <v>5.001302661134483</v>
       </c>
       <c r="E29" t="n">
-        <v>4.688974153201285</v>
+        <v>4.990104247569951</v>
       </c>
       <c r="F29" t="n">
-        <v>4.464975338828223</v>
+        <v>2.346794759149375</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01736174326801005</v>
+        <v>0.1096612102155224</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7525074441666898</v>
+        <v>-0.1682322270009599</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.875156268253492</v>
+        <v>-0.5423393239366984</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9542768261190366</v>
+        <v>-0.7230503951075881</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.182943445657183</v>
+        <v>-0.9702863778691507</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.2922060610149792</v>
+        <v>-0.4959904052820434</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.06347631830723849</v>
+        <v>-0.01878746909365599</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62.25845640745723</v>
+        <v>51.19230998678657</v>
       </c>
       <c r="B30" t="n">
-        <v>50.08523125257215</v>
+        <v>33.87377462782014</v>
       </c>
       <c r="C30" t="n">
-        <v>6.21528066565252</v>
+        <v>5.00510251015473</v>
       </c>
       <c r="D30" t="n">
-        <v>6.761157559525011</v>
+        <v>5.000841962544721</v>
       </c>
       <c r="E30" t="n">
-        <v>2.833629194702182</v>
+        <v>4.996203567782921</v>
       </c>
       <c r="F30" t="n">
-        <v>4.851855330062083</v>
+        <v>3.544604489987958</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01445798497814656</v>
+        <v>0.03363369106274416</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7858723442626794</v>
+        <v>-0.6626208881818388</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8987107173910293</v>
+        <v>-0.827697854703878</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9625616890816845</v>
+        <v>-0.918098711483377</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1157046232155891</v>
+        <v>-0.9365212869581482</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3527442434783755</v>
+        <v>-0.469634395459104</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3904355259521449</v>
+        <v>-0.01748043443818206</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>61.33463738550354</v>
+        <v>72.74346376769985</v>
       </c>
       <c r="B31" t="n">
-        <v>50.08523125257215</v>
+        <v>105.1075451445388</v>
       </c>
       <c r="C31" t="n">
-        <v>5.091128062582961</v>
+        <v>33.75067277097235</v>
       </c>
       <c r="D31" t="n">
-        <v>5.045233486515854</v>
+        <v>13.69998754043308</v>
       </c>
       <c r="E31" t="n">
-        <v>4.711709179540781</v>
+        <v>4.112247835818187</v>
       </c>
       <c r="F31" t="n">
-        <v>4.542719424620951</v>
+        <v>5.375837598804137</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01522884381490873</v>
+        <v>0.009386561944050907</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7765843685976712</v>
+        <v>-0.8772943590378357</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8921867499389876</v>
+        <v>-0.9548423056114955</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9602546400854782</v>
+        <v>-0.9799121371027384</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.5586553429689848</v>
+        <v>-0.03875949538156926</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3293837760076935</v>
+        <v>-0.418398746742108</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.05917102609124069</v>
+        <v>-0.0971522625273884</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>51.35223671980444</v>
+        <v>82.77840043902704</v>
       </c>
       <c r="B32" t="n">
-        <v>35.08127606436906</v>
+        <v>187.9914422325716</v>
       </c>
       <c r="C32" t="n">
-        <v>5.085424344090376</v>
+        <v>33.44112276894163</v>
       </c>
       <c r="D32" t="n">
-        <v>5.00003373679732</v>
+        <v>12.01718371737172</v>
       </c>
       <c r="E32" t="n">
-        <v>4.711787341871741</v>
+        <v>4.029155673765287</v>
       </c>
       <c r="F32" t="n">
-        <v>3.554971250270905</v>
+        <v>6.264851152486162</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02987007659148068</v>
+        <v>0.005758438218519515</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6234986859380724</v>
+        <v>-0.9159039219156083</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7873901961076439</v>
+        <v>-0.9876501066390209</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9191142189265417</v>
+        <v>-0.9880204219372712</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.642890722496729</v>
+        <v>-0.00479935521577841</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4852736141313116</v>
+        <v>-0.4933604234124578</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.06011426298684748</v>
+        <v>-0.04251790972068843</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87.29509583191253</v>
+        <v>37.12303862370963</v>
       </c>
       <c r="B33" t="n">
-        <v>64.60618560531475</v>
+        <v>48.22308542359199</v>
       </c>
       <c r="C33" t="n">
-        <v>33.91256137085352</v>
+        <v>5.072487657659277</v>
       </c>
       <c r="D33" t="n">
-        <v>9.318874470426419</v>
+        <v>5.001247312419832</v>
       </c>
       <c r="E33" t="n">
-        <v>4.47169072986489</v>
+        <v>4.962051837916606</v>
       </c>
       <c r="F33" t="n">
-        <v>7.226422515334507</v>
+        <v>2.283947546800645</v>
       </c>
       <c r="G33" t="n">
-        <v>0.004250797563697085</v>
+        <v>0.1171190785482963</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9190949193055966</v>
+        <v>-0.1256597018265291</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9970172957032336</v>
+        <v>-0.5194871295093724</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9903138707935579</v>
+        <v>-0.7038337452358852</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.2157163348265365</v>
+        <v>-0.5362678104034476</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.3950098841441616</v>
+        <v>-0.5210043354326394</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1206469948796178</v>
+        <v>-0.02258990476733824</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>78.30567166696609</v>
+        <v>35.54819326918227</v>
       </c>
       <c r="B34" t="n">
-        <v>37.35798056938457</v>
+        <v>42.22838215294913</v>
       </c>
       <c r="C34" t="n">
-        <v>5.030374521842911</v>
+        <v>5.005379601047423</v>
       </c>
       <c r="D34" t="n">
-        <v>5.029766937084531</v>
+        <v>5.007910403956627</v>
       </c>
       <c r="E34" t="n">
-        <v>4.888866943191124</v>
+        <v>4.995440612557521</v>
       </c>
       <c r="F34" t="n">
-        <v>6.090542488451299</v>
+        <v>2.148063165958346</v>
       </c>
       <c r="G34" t="n">
-        <v>0.006174335444353998</v>
+        <v>0.1387965306662321</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8901325469154657</v>
+        <v>-0.005323381634809397</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9756746612393522</v>
+        <v>-0.4570175640908928</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9850398218261459</v>
+        <v>-0.6477593194649863</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.09373343113985075</v>
+        <v>-0.04495002851542177</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5336365771730255</v>
+        <v>-0.5375372937083699</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.04215231938091373</v>
+        <v>-0.01753742483999346</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>148.8071153738823</v>
+        <v>53.56422259289461</v>
       </c>
       <c r="B35" t="n">
-        <v>52.26419655048052</v>
+        <v>47.06048077114853</v>
       </c>
       <c r="C35" t="n">
-        <v>33.61269682336419</v>
+        <v>5.00365763450952</v>
       </c>
       <c r="D35" t="n">
-        <v>17.67231874242398</v>
+        <v>5.415818090965578</v>
       </c>
       <c r="E35" t="n">
-        <v>2.48562633815522</v>
+        <v>4.995375358487403</v>
       </c>
       <c r="F35" t="n">
-        <v>12.50317157146102</v>
+        <v>3.731140948632603</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0007476970941704837</v>
+        <v>0.02829368041382382</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9810374038382361</v>
+        <v>-0.7047135268868547</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.035746624344951</v>
+        <v>-0.8541163052429834</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9988528641554361</v>
+        <v>-0.9316701578113221</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.004843200865050116</v>
+        <v>-0.4675180312322673</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2321327042055751</v>
+        <v>-0.5270640122279466</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.07101891530488443</v>
+        <v>-0.01944252141354318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116.4468318565791</v>
+        <v>106.7494757739159</v>
       </c>
       <c r="B36" t="n">
-        <v>37.39698247856499</v>
+        <v>41.23076432170562</v>
       </c>
       <c r="C36" t="n">
-        <v>33.74841014983256</v>
+        <v>34.89526285481629</v>
       </c>
       <c r="D36" t="n">
-        <v>5.055485520763119</v>
+        <v>7.18670339754016</v>
       </c>
       <c r="E36" t="n">
-        <v>3.130880539710778</v>
+        <v>4.873650464152623</v>
       </c>
       <c r="F36" t="n">
-        <v>10.1281437426292</v>
+        <v>8.897742213393967</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001550019063245402</v>
+        <v>0.00227544311902612</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9641678079519864</v>
+        <v>-0.959507885102076</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.029036418625027</v>
+        <v>-1.025717287567712</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9969408629553548</v>
+        <v>-0.9956684170218993</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3276923435355645</v>
+        <v>-0.02975184336287256</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6479381577706433</v>
+        <v>-0.6724260276657311</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.09670073631693139</v>
+        <v>-0.1303527564451236</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>58.16401973482688</v>
+        <v>57.54799731997752</v>
       </c>
       <c r="B37" t="n">
-        <v>84.43140221303452</v>
+        <v>42.82235578171909</v>
       </c>
       <c r="C37" t="n">
-        <v>39.67498179017567</v>
+        <v>5.296964667743065</v>
       </c>
       <c r="D37" t="n">
-        <v>8.379066955623351</v>
+        <v>5.000005091643331</v>
       </c>
       <c r="E37" t="n">
-        <v>4.972653045003717</v>
+        <v>4.316667618096615</v>
       </c>
       <c r="F37" t="n">
-        <v>4.211159106208094</v>
+        <v>4.250944727751516</v>
       </c>
       <c r="G37" t="n">
-        <v>0.01900189210105135</v>
+        <v>0.02149790377325235</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7373068782727391</v>
+        <v>-0.7609553064993134</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8638522668121873</v>
+        <v>-0.8926907518364708</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9508535684586118</v>
+        <v>-0.9487151861570884</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.04356401977359366</v>
+        <v>-2.86650506515596</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6362126961713638</v>
+        <v>-0.3617358177852607</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.08750295251718895</v>
+        <v>-0.1371721930154561</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42.07079527919285</v>
+        <v>85.05263843434814</v>
       </c>
       <c r="B38" t="n">
-        <v>48.13271529881845</v>
+        <v>47.24130081265413</v>
       </c>
       <c r="C38" t="n">
-        <v>5.060930801501402</v>
+        <v>5.002307525188756</v>
       </c>
       <c r="D38" t="n">
-        <v>5.003158747897634</v>
+        <v>5.001353438601298</v>
       </c>
       <c r="E38" t="n">
-        <v>4.705676773226432</v>
+        <v>4.913037817590243</v>
       </c>
       <c r="F38" t="n">
-        <v>2.738337169622746</v>
+        <v>7.117730511688422</v>
       </c>
       <c r="G38" t="n">
-        <v>0.06437746115265125</v>
+        <v>0.00502346199103866</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3211706627881916</v>
+        <v>-0.9232246246441054</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6002419785605163</v>
+        <v>-1.006267869344368</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8204494435559658</v>
+        <v>-0.9892512371712757</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.5407864367297265</v>
+        <v>-4.786692238889572</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.4240852904357681</v>
+        <v>-0.2349680603260081</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.06156792119531081</v>
+        <v>-0.0363814841282361</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>100.9888760981098</v>
+        <v>64.01229450016561</v>
       </c>
       <c r="B39" t="n">
-        <v>32.77502823178106</v>
+        <v>116.9193002070638</v>
       </c>
       <c r="C39" t="n">
-        <v>39.8824066771232</v>
+        <v>33.44516442029966</v>
       </c>
       <c r="D39" t="n">
-        <v>9.319289974710271</v>
+        <v>14.76836372304748</v>
       </c>
       <c r="E39" t="n">
-        <v>4.973304943794354</v>
+        <v>4.120922307503569</v>
       </c>
       <c r="F39" t="n">
-        <v>8.32574194863534</v>
+        <v>4.665701078443656</v>
       </c>
       <c r="G39" t="n">
-        <v>0.002554520327788295</v>
+        <v>0.01532384113162278</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9464234508027862</v>
+        <v>-0.8212343921730699</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.016963476019301</v>
+        <v>-0.9093292317617266</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9945922639415815</v>
+        <v>-0.9664991316827133</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.1929554010123916</v>
+        <v>-0.01215297340895511</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6293939464011873</v>
+        <v>-0.353176303489715</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.09023689615116215</v>
+        <v>-0.04323410052831916</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>107.6547868793855</v>
+        <v>37.23743200117975</v>
       </c>
       <c r="B40" t="n">
-        <v>32.89039740021303</v>
+        <v>41.2490903026748</v>
       </c>
       <c r="C40" t="n">
-        <v>32.4630473361341</v>
+        <v>5.074355857557061</v>
       </c>
       <c r="D40" t="n">
-        <v>8.959755619978925</v>
+        <v>5.000290713668953</v>
       </c>
       <c r="E40" t="n">
-        <v>4.462296674927356</v>
+        <v>4.983673686919939</v>
       </c>
       <c r="F40" t="n">
-        <v>9.228748637743703</v>
+        <v>2.305172093424995</v>
       </c>
       <c r="G40" t="n">
-        <v>0.002040807827424497</v>
+        <v>0.1157019905418311</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9552840638071984</v>
+        <v>-0.1336563091780768</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.023160807196804</v>
+        <v>-0.5240004111737196</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9958122932679697</v>
+        <v>-0.7074563002101886</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.2946264098217456</v>
+        <v>-0.8622245454127676</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.6791887647508781</v>
+        <v>-0.5011010311287561</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.02738610990024489</v>
+        <v>-0.01845314528827481</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37.73977163657244</v>
+        <v>86.56657292631303</v>
       </c>
       <c r="B41" t="n">
-        <v>47.99017213540045</v>
+        <v>197.9607363282337</v>
       </c>
       <c r="C41" t="n">
-        <v>5.77561042171504</v>
+        <v>33.67755737172249</v>
       </c>
       <c r="D41" t="n">
-        <v>5.076958893241468</v>
+        <v>17.35021187039951</v>
       </c>
       <c r="E41" t="n">
-        <v>4.679665808278139</v>
+        <v>4.096801274000342</v>
       </c>
       <c r="F41" t="n">
-        <v>2.384798335392432</v>
+        <v>7.359521595128566</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09829254907590387</v>
+        <v>0.004956154499280194</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.06269536130298055</v>
+        <v>-0.9257103288841901</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4543546284588962</v>
+        <v>-0.9958430404882789</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7227238146473179</v>
+        <v>-0.9899836672485846</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.9644693854752598</v>
+        <v>-0.5730544164834332</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4964334628414849</v>
+        <v>-0.5216583360415258</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.06894911181497528</v>
+        <v>-0.08256143308240538</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>98.23659959984047</v>
+        <v>56.73344089250674</v>
       </c>
       <c r="B42" t="n">
-        <v>32.88576420687859</v>
+        <v>48.22308542359199</v>
       </c>
       <c r="C42" t="n">
-        <v>33.52721296797106</v>
+        <v>5.335814904883349</v>
       </c>
       <c r="D42" t="n">
-        <v>10.8916371143506</v>
+        <v>5.003675774550048</v>
       </c>
       <c r="E42" t="n">
-        <v>4.9855562648692</v>
+        <v>4.464838362208695</v>
       </c>
       <c r="F42" t="n">
-        <v>8.095194648878698</v>
+        <v>4.137993686825497</v>
       </c>
       <c r="G42" t="n">
-        <v>0.002824896467569073</v>
+        <v>0.02269990202382039</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.9419933727440077</v>
+        <v>-0.7507195336131648</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.01371116934334</v>
+        <v>-0.8855718234187485</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9939602862291442</v>
+        <v>-0.9457058367186081</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.1981263639481306</v>
+        <v>-2.398127244663752</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6088342490430397</v>
+        <v>-0.3955402250751374</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.05677351808378685</v>
+        <v>-0.1072190634966752</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>93.91655628384584</v>
+        <v>52.146007806255</v>
       </c>
       <c r="B43" t="n">
-        <v>30.21977320322515</v>
+        <v>34.18229417182832</v>
       </c>
       <c r="C43" t="n">
-        <v>33.67987641656241</v>
+        <v>5.080131249698384</v>
       </c>
       <c r="D43" t="n">
-        <v>9.66402364698947</v>
+        <v>5.000035663159764</v>
       </c>
       <c r="E43" t="n">
-        <v>4.974945177662397</v>
+        <v>4.986416529878878</v>
       </c>
       <c r="F43" t="n">
-        <v>7.612823981746976</v>
+        <v>3.607340698612592</v>
       </c>
       <c r="G43" t="n">
-        <v>0.003293184586173121</v>
+        <v>0.03133955080658265</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.9342130059363464</v>
+        <v>-0.6804743812752138</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.008147303949184</v>
+        <v>-0.8388035354659894</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.992769954939241</v>
+        <v>-0.923927904259824</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01014574750009798</v>
+        <v>-0.6283914194994085</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5046292643666088</v>
+        <v>-0.4970002982363314</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.08302421914501099</v>
+        <v>-0.01738260354874659</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>48.5850387947747</v>
+        <v>47.62740274683826</v>
       </c>
       <c r="B44" t="n">
-        <v>48.02516482081347</v>
+        <v>42.15052469952055</v>
       </c>
       <c r="C44" t="n">
-        <v>33.68932815646495</v>
+        <v>5.014198526691136</v>
       </c>
       <c r="D44" t="n">
-        <v>5.076958893241468</v>
+        <v>5.002875604561468</v>
       </c>
       <c r="E44" t="n">
-        <v>4.975829452422918</v>
+        <v>4.99880574071498</v>
       </c>
       <c r="F44" t="n">
-        <v>3.375605096941867</v>
+        <v>3.346237027386307</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03715539921613199</v>
+        <v>0.0443812172485212</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5558736950253191</v>
+        <v>-0.5825576991065763</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7433550193083218</v>
+        <v>-0.7793429365836069</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.899051603030668</v>
+        <v>-0.8906844241946144</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2249882042466569</v>
+        <v>-2.989556954093045</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.7115004127901979</v>
+        <v>-0.3215777025900584</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.08491039806615704</v>
+        <v>-0.01709086309754859</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37.53891608900738</v>
+        <v>78.34398547829885</v>
       </c>
       <c r="B45" t="n">
-        <v>51.78307374408875</v>
+        <v>124.3771251353847</v>
       </c>
       <c r="C45" t="n">
-        <v>5.009162393422741</v>
+        <v>33.44516442029966</v>
       </c>
       <c r="D45" t="n">
-        <v>5.000463504373037</v>
+        <v>14.76836372304748</v>
       </c>
       <c r="E45" t="n">
-        <v>4.985371222679827</v>
+        <v>3.873921020135393</v>
       </c>
       <c r="F45" t="n">
-        <v>2.31293869602699</v>
+        <v>6.097254612288435</v>
       </c>
       <c r="G45" t="n">
-        <v>0.100318758548746</v>
+        <v>0.007129012462337352</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.04782452258482435</v>
+        <v>-0.9010346466998822</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4462804723801176</v>
+        <v>-0.974742840192279</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.716741645298685</v>
+        <v>-0.9850690652254702</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.2748295105406053</v>
+        <v>-0.2631130927407944</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5116737076995882</v>
+        <v>-0.4602350344443274</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.01831544700933687</v>
+        <v>-0.04323410052831916</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>39.02934850707268</v>
+        <v>71.39122492594207</v>
       </c>
       <c r="B46" t="n">
-        <v>39.78873698997671</v>
+        <v>178.7430579571399</v>
       </c>
       <c r="C46" t="n">
-        <v>5.009954939651355</v>
+        <v>33.44444018203355</v>
       </c>
       <c r="D46" t="n">
-        <v>5.000044481616169</v>
+        <v>13.73312671645789</v>
       </c>
       <c r="E46" t="n">
-        <v>4.985043666815723</v>
+        <v>4.548369810309505</v>
       </c>
       <c r="F46" t="n">
-        <v>2.484742380730308</v>
+        <v>5.241213126028298</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0861509093726326</v>
+        <v>0.0100763424702592</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1519481059883217</v>
+        <v>-0.8703738599620355</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5035889653481465</v>
+        <v>-0.9491049648497889</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7575934031552692</v>
+        <v>-0.9783463901356361</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.87578705726179</v>
+        <v>-0.00729018672570836</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4450562407361245</v>
+        <v>-0.4082974283026435</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.01847845318966949</v>
+        <v>-0.04310576368212005</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123.1177966800262</v>
+        <v>55.27973822693369</v>
       </c>
       <c r="B47" t="n">
-        <v>34.71422033001886</v>
+        <v>47.18871693531933</v>
       </c>
       <c r="C47" t="n">
-        <v>5.02542379317784</v>
+        <v>5.014733082976048</v>
       </c>
       <c r="D47" t="n">
-        <v>5.660776571918974</v>
+        <v>5.00028911716211</v>
       </c>
       <c r="E47" t="n">
-        <v>4.965059412984999</v>
+        <v>4.762893682042064</v>
       </c>
       <c r="F47" t="n">
-        <v>11.02963522452354</v>
+        <v>3.926327053345383</v>
       </c>
       <c r="G47" t="n">
-        <v>0.001283651671585543</v>
+        <v>0.02506379559957097</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.9692969096102858</v>
+        <v>-0.7309418235439226</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.032058645408888</v>
+        <v>-0.8719498899428894</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9975519160688087</v>
+        <v>-0.9397654415561015</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.541095713095685</v>
+        <v>-1.579799245997362</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3686764920238964</v>
+        <v>-0.4558694488441979</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.01954416326371918</v>
+        <v>-0.04995689984411757</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>94.29844329194627</v>
+        <v>65.34808182192532</v>
       </c>
       <c r="B48" t="n">
-        <v>30.21977320322515</v>
+        <v>116.9193002070638</v>
       </c>
       <c r="C48" t="n">
-        <v>33.52721296797106</v>
+        <v>33.44516442029966</v>
       </c>
       <c r="D48" t="n">
-        <v>10.8916371143506</v>
+        <v>14.76836372304748</v>
       </c>
       <c r="E48" t="n">
-        <v>4.9855562648692</v>
+        <v>4.142135307794531</v>
       </c>
       <c r="F48" t="n">
-        <v>7.690576541711274</v>
+        <v>4.786948389246708</v>
       </c>
       <c r="G48" t="n">
-        <v>0.003261915901549175</v>
+        <v>0.0141598010362242</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.9348620011389076</v>
+        <v>-0.8317677418128743</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.008520447581982</v>
+        <v>-0.9176884659259166</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9928863654728407</v>
+        <v>-0.9691554622822793</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.1438482362407336</v>
+        <v>-0.03555341835383077</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.542533063398101</v>
+        <v>-0.3631547279276303</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.05677351808378685</v>
+        <v>-0.04323410052831916</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>144.0315721934133</v>
+        <v>54.98098198390451</v>
       </c>
       <c r="B49" t="n">
-        <v>34.979273798571</v>
+        <v>37.94496546275383</v>
       </c>
       <c r="C49" t="n">
-        <v>33.91256137085352</v>
+        <v>5.014205369616961</v>
       </c>
       <c r="D49" t="n">
-        <v>18.88988417531437</v>
+        <v>5.027800982708914</v>
       </c>
       <c r="E49" t="n">
-        <v>4.47169072986489</v>
+        <v>4.90529500523233</v>
       </c>
       <c r="F49" t="n">
-        <v>12.00795426701027</v>
+        <v>3.887757748433112</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0008368220843535904</v>
+        <v>0.02558956659335718</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.9792453258133984</v>
+        <v>-0.726611805652755</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.035008233700354</v>
+        <v>-0.8689880166588164</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9986929902208247</v>
+        <v>-0.9384455190962907</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.06042995078096974</v>
+        <v>-1.377547546182818</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.1845678501303153</v>
+        <v>-0.4682679486646587</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1206469948796178</v>
+        <v>-0.0388277914728801</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>143.8466633642419</v>
+        <v>38.10572189411168</v>
       </c>
       <c r="B50" t="n">
-        <v>34.979273798571</v>
+        <v>48.39266954084323</v>
       </c>
       <c r="C50" t="n">
-        <v>33.91256137085352</v>
+        <v>5.02824927440536</v>
       </c>
       <c r="D50" t="n">
-        <v>18.88988417531437</v>
+        <v>5.039926497539008</v>
       </c>
       <c r="E50" t="n">
-        <v>4.465411555004947</v>
+        <v>4.998528454620946</v>
       </c>
       <c r="F50" t="n">
-        <v>11.98305372793441</v>
+        <v>2.387676378255463</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0008404143505883386</v>
+        <v>0.105718343390242</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.9791726718894102</v>
+        <v>-0.1910514344478638</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.034979453382643</v>
+        <v>-0.5546961382540017</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9986862568273217</v>
+        <v>-0.7332227028983108</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.05749025257473096</v>
+        <v>-1.201590539033962</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.1827261410001926</v>
+        <v>-0.4818538684867769</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1206469948796178</v>
+        <v>-0.01560581920095328</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49.57589541141962</v>
+        <v>65.34709887476542</v>
       </c>
       <c r="B51" t="n">
-        <v>44.51763884784168</v>
+        <v>42.28813155864844</v>
       </c>
       <c r="C51" t="n">
-        <v>30.65428929144456</v>
+        <v>5.004460313292632</v>
       </c>
       <c r="D51" t="n">
-        <v>5.037316577564255</v>
+        <v>5.000011549022557</v>
       </c>
       <c r="E51" t="n">
-        <v>4.972493846170532</v>
+        <v>4.990517383153158</v>
       </c>
       <c r="F51" t="n">
-        <v>3.514351262464928</v>
+        <v>4.954462017685426</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03436949210685721</v>
+        <v>0.01329366003721853</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5816268912449912</v>
+        <v>-0.8352620516659208</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7599117981388892</v>
+        <v>-0.942981035521241</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9068833432879368</v>
+        <v>-0.9691536063936259</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.3590178418830306</v>
+        <v>-0.856149967936997</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.6644719916391691</v>
+        <v>-0.3060353327396529</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1758096125341451</v>
+        <v>-0.0173483512186389</v>
       </c>
     </row>
   </sheetData>

--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_01/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_01/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>41.58539580037238</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="B2" t="n">
-        <v>50.8971335744869</v>
+        <v>80.61516756635106</v>
       </c>
       <c r="C2" t="n">
-        <v>38.77984425368555</v>
+        <v>38.57584868507296</v>
       </c>
       <c r="D2" t="n">
-        <v>5.135975027281729</v>
+        <v>10.73401710436499</v>
       </c>
       <c r="E2" t="n">
-        <v>3.89643038967155</v>
+        <v>3.910354674819244</v>
       </c>
       <c r="F2" t="n">
-        <v>2.793360096413218</v>
+        <v>8.372916002320084</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1115737233033311</v>
+        <v>0.004820128791114395</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02684515684840028</v>
+        <v>-0.9143877316863999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5138830542975749</v>
+        <v>-0.9560268237307779</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7285923257103165</v>
+        <v>-0.9888840454047049</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.005153496846184669</v>
+        <v>-0.0001584898301321876</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5765895941951806</v>
+        <v>-0.5874999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-8.980708116543741e-05</v>
+        <v>-0.001031359850357794</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999999997461</v>
+        <v>43.30032901240965</v>
       </c>
       <c r="B3" t="n">
-        <v>49.19924568799134</v>
+        <v>49.3467117491757</v>
       </c>
       <c r="C3" t="n">
-        <v>38.78143072440289</v>
+        <v>38.59265056441485</v>
       </c>
       <c r="D3" t="n">
-        <v>9.666369694400988</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="E3" t="n">
-        <v>4.13208020684216</v>
+        <v>4.239455103404638</v>
       </c>
       <c r="F3" t="n">
-        <v>8.196352075705384</v>
+        <v>2.987834308316526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004893964367908548</v>
+        <v>0.09428715733743846</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9250445081380844</v>
+        <v>-0.01085332637437773</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9619546423073063</v>
+        <v>-0.506837675082949</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9906473135382766</v>
+        <v>-0.7230904993390085</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.354652978652985e-05</v>
+        <v>-3.249956790546093e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069729938464</v>
+        <v>-0.3112871685160238</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0004129971657187009</v>
+        <v>-0.004951798363465321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78.69233822841231</v>
+        <v>89.73904648563129</v>
       </c>
       <c r="B4" t="n">
-        <v>71.17736373385175</v>
+        <v>69.94972180123544</v>
       </c>
       <c r="C4" t="n">
-        <v>33.96398306354471</v>
+        <v>38.58692645642956</v>
       </c>
       <c r="D4" t="n">
-        <v>5.000321133319375</v>
+        <v>12.69221178447858</v>
       </c>
       <c r="E4" t="n">
-        <v>4.447581698074349</v>
+        <v>4.170150673109505</v>
       </c>
       <c r="F4" t="n">
-        <v>6.301975600675576</v>
+        <v>7.235121799841389</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01072700862821388</v>
+        <v>0.00702657250945196</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8512934783360941</v>
+        <v>-0.8827240006057034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9244697929940017</v>
+        <v>-0.9391598920523179</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9772256519342502</v>
+        <v>-0.9832045660944759</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3125678215103621</v>
+        <v>-0.005851057284745895</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5208941831308727</v>
+        <v>-0.5143907062101228</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.123819213742151</v>
+        <v>-0.003616173166898079</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60.85119787004918</v>
+        <v>82.53941248171894</v>
       </c>
       <c r="B5" t="n">
-        <v>52.7643863595871</v>
+        <v>70.87724168158313</v>
       </c>
       <c r="C5" t="n">
-        <v>38.77945913626736</v>
+        <v>38.59442637245613</v>
       </c>
       <c r="D5" t="n">
-        <v>5.005541063999845</v>
+        <v>13.15512192224495</v>
       </c>
       <c r="E5" t="n">
-        <v>4.712433622424912</v>
+        <v>2.762385130379323</v>
       </c>
       <c r="F5" t="n">
-        <v>4.524619914442661</v>
+        <v>6.414952775546492</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02683265466917092</v>
+        <v>0.009443072134486648</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6845497667154345</v>
+        <v>-0.8515732107707384</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8286661334543043</v>
+        <v>-0.9242778256964475</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9388202468353603</v>
+        <v>-0.9772551830378055</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.03278359211743798</v>
+        <v>-0.002393004348623359</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4459939186328383</v>
+        <v>-0.4232921257921794</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.135235169260155e-05</v>
+        <v>-0.005366153573097832</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84.20418160006189</v>
+        <v>85.64434845055487</v>
       </c>
       <c r="B6" t="n">
-        <v>71.1732992607799</v>
+        <v>67.85644738271596</v>
       </c>
       <c r="C6" t="n">
-        <v>38.78107698650008</v>
+        <v>38.59442637245613</v>
       </c>
       <c r="D6" t="n">
-        <v>11.33680975847045</v>
+        <v>13.37424789082932</v>
       </c>
       <c r="E6" t="n">
-        <v>4.870186871492728</v>
+        <v>2.640470117695155</v>
       </c>
       <c r="F6" t="n">
-        <v>6.668804963025414</v>
+        <v>6.810713748494469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008823462568485662</v>
+        <v>0.008296311612024572</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8768982671474413</v>
+        <v>-0.8667111660609859</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9364378220500409</v>
+        <v>-0.9317254648098191</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9821194649683752</v>
+        <v>-0.9802487015567761</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002340325782788143</v>
+        <v>-0.1147931211894494</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4861356290780675</v>
+        <v>-0.2887449004759555</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0003409349577809926</v>
+        <v>-0.005366153573097832</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42.35068256341448</v>
+        <v>52.73450039580228</v>
       </c>
       <c r="B7" t="n">
-        <v>62.43190606159103</v>
+        <v>52.69677123872517</v>
       </c>
       <c r="C7" t="n">
-        <v>38.78115582199445</v>
+        <v>22.72751424484366</v>
       </c>
       <c r="D7" t="n">
-        <v>6.723422095195338</v>
+        <v>5.065314158702109</v>
       </c>
       <c r="E7" t="n">
-        <v>4.977662559601859</v>
+        <v>4.015359095992242</v>
       </c>
       <c r="F7" t="n">
-        <v>2.917997112034945</v>
+        <v>3.846056962752981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1050066835147328</v>
+        <v>0.04442490356314666</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07692899706515881</v>
+        <v>-0.448817725556537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5351721388756638</v>
+        <v>-0.7058515238338925</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7466673873864624</v>
+        <v>-0.8723531913860978</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.002041459100598911</v>
+        <v>-0.009081311115012945</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7011354598827296</v>
+        <v>-0.4428656076836504</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0003569950399578988</v>
+        <v>-5.313386560609756e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.82958000566246</v>
+        <v>93.63338885983623</v>
       </c>
       <c r="B8" t="n">
-        <v>50.32408416824362</v>
+        <v>64.40941820632641</v>
       </c>
       <c r="C8" t="n">
-        <v>38.79052233246561</v>
+        <v>38.80579123827384</v>
       </c>
       <c r="D8" t="n">
-        <v>5.005422882041837</v>
+        <v>12.52665437431478</v>
       </c>
       <c r="E8" t="n">
-        <v>4.70589332277696</v>
+        <v>4.440173068986787</v>
       </c>
       <c r="F8" t="n">
-        <v>4.749179182889494</v>
+        <v>7.728412849699273</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02386920528019153</v>
+        <v>0.006065290449197215</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7128975435804006</v>
+        <v>-0.896329229854875</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.844587952360175</v>
+        <v>-0.9462511036241501</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9459633428050878</v>
+        <v>-0.9857103489060324</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1924463011685562</v>
+        <v>-0.09322566694899762</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4321708211736951</v>
+        <v>-0.5421378956263331</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.002265106723365593</v>
+        <v>-0.05468462226389553</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47.6687645109844</v>
+        <v>48.26364949316594</v>
       </c>
       <c r="B9" t="n">
-        <v>47.43351881256253</v>
+        <v>43.45151143926235</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82246614072967</v>
+        <v>38.57578141323977</v>
       </c>
       <c r="D9" t="n">
-        <v>5.002001064196033</v>
+        <v>5.06480173798276</v>
       </c>
       <c r="E9" t="n">
-        <v>4.550340007065007</v>
+        <v>4.522430845243965</v>
       </c>
       <c r="F9" t="n">
-        <v>3.268426556460547</v>
+        <v>3.359678855624304</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06645187913585965</v>
+        <v>0.06208573903414958</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3511173544399506</v>
+        <v>-0.2839751046448813</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6589809446239854</v>
+        <v>-0.6276179718590382</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8413497710253172</v>
+        <v>-0.819663944694648</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.005910039195199493</v>
+        <v>-0.1407962628354549</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7254533567032549</v>
+        <v>-0.1177176697665283</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.008772583968899012</v>
+        <v>-0.001015663089278668</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49.83375552224673</v>
+        <v>51.54693186947154</v>
       </c>
       <c r="B10" t="n">
-        <v>47.62094931507971</v>
+        <v>52.89992239742097</v>
       </c>
       <c r="C10" t="n">
-        <v>38.7810721627917</v>
+        <v>38.58666831665043</v>
       </c>
       <c r="D10" t="n">
-        <v>5.156873805694705</v>
+        <v>5.005691713566158</v>
       </c>
       <c r="E10" t="n">
-        <v>4.576260346223205</v>
+        <v>2.028184271270521</v>
       </c>
       <c r="F10" t="n">
-        <v>3.533536823055653</v>
+        <v>3.738737757132678</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05619624178215379</v>
+        <v>0.04842980309959305</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4311741720316132</v>
+        <v>-0.4102269060171977</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6973714888519212</v>
+        <v>-0.687022816464815</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.866728989736707</v>
+        <v>-0.8603735856185682</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3726847460941762</v>
+        <v>-0.2285770205900728</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6772537675492909</v>
+        <v>-0.4948217307106201</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0003399522893335422</v>
+        <v>-0.003555940551766973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>70.9140931174709</v>
+        <v>44.4933930720697</v>
       </c>
       <c r="B11" t="n">
-        <v>52.23965608770153</v>
+        <v>49.3632235416372</v>
       </c>
       <c r="C11" t="n">
-        <v>33.55903793918537</v>
+        <v>38.59327473136232</v>
       </c>
       <c r="D11" t="n">
-        <v>6.393408329323115</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="E11" t="n">
-        <v>4.357714591003689</v>
+        <v>4.239455103404638</v>
       </c>
       <c r="F11" t="n">
-        <v>5.479471531496048</v>
+        <v>3.111244976628612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01555863701099911</v>
+        <v>0.08497250812354494</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7984005926536396</v>
+        <v>-0.08771039322093713</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8945788719210012</v>
+        <v>-0.5398388361513019</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9660274302549929</v>
+        <v>-0.7512676497060805</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06580636172501445</v>
+        <v>-0.007580915110783304</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7200157215033329</v>
+        <v>-0.3092510632613515</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.06165599725276619</v>
+        <v>-0.005097437317874293</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>50.86435286152285</v>
+        <v>46.3123386716366</v>
       </c>
       <c r="B12" t="n">
-        <v>44.09584585180684</v>
+        <v>46.67277253472324</v>
       </c>
       <c r="C12" t="n">
-        <v>38.78115353138588</v>
+        <v>38.58982217915301</v>
       </c>
       <c r="D12" t="n">
-        <v>5.000000040491829</v>
+        <v>5.841805456188386</v>
       </c>
       <c r="E12" t="n">
-        <v>4.623471593981765</v>
+        <v>4.621343159001262</v>
       </c>
       <c r="F12" t="n">
-        <v>3.635758843820103</v>
+        <v>3.236939346998387</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05199779744257826</v>
+        <v>0.07279378643753671</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4646978060659843</v>
+        <v>-0.1903529068627156</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.713838671924627</v>
+        <v>-0.5850753787062808</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8770320882067106</v>
+        <v>-0.7877177600405837</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4892408347358523</v>
+        <v>-0.005117004015083011</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6391096519785154</v>
+        <v>-0.2401311304778092</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0003565284054545009</v>
+        <v>-0.004291841802369217</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68.67802245334211</v>
+        <v>66.16540818638909</v>
       </c>
       <c r="B13" t="n">
-        <v>48.8416496049929</v>
+        <v>49.08665638158412</v>
       </c>
       <c r="C13" t="n">
-        <v>40.20958258331228</v>
+        <v>38.57836854243416</v>
       </c>
       <c r="D13" t="n">
-        <v>6.836893813129748</v>
+        <v>7.896503730860078</v>
       </c>
       <c r="E13" t="n">
-        <v>4.985375317690747</v>
+        <v>4.695975935405031</v>
       </c>
       <c r="F13" t="n">
-        <v>5.277805141171593</v>
+        <v>5.085634841496567</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01750325862122225</v>
+        <v>0.01969007282272705</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.77846205145001</v>
+        <v>-0.7177144797603594</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8825364119030055</v>
+        <v>-0.8472528809726347</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9615272694413045</v>
+        <v>-0.9472215941925793</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1306909189890425</v>
+        <v>-0.06494525015737651</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7060263259030003</v>
+        <v>-0.1309525926220987</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08441774662407572</v>
+        <v>-0.001619326567970508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>65.82450016431187</v>
+        <v>64.021747047492</v>
       </c>
       <c r="B14" t="n">
-        <v>48.8416496049929</v>
+        <v>54.00439990266294</v>
       </c>
       <c r="C14" t="n">
-        <v>38.78002828107132</v>
+        <v>38.57591495081201</v>
       </c>
       <c r="D14" t="n">
-        <v>6.836893813129748</v>
+        <v>8.775455893239117</v>
       </c>
       <c r="E14" t="n">
-        <v>4.977916716747085</v>
+        <v>2.104702268816882</v>
       </c>
       <c r="F14" t="n">
-        <v>4.982000783405132</v>
+        <v>4.929354907068518</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02036692697504397</v>
+        <v>0.02227568462078713</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7491681742690809</v>
+        <v>-0.6878412502607547</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8652814189323628</v>
+        <v>-0.8300596136352202</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9547068171579715</v>
+        <v>-0.9395630993682988</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04111051949471743</v>
+        <v>-0.04656992499514954</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6317556676538434</v>
+        <v>-0.655471064634116</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0001272964755297312</v>
+        <v>-0.001046821856135749</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>42.95742512134367</v>
+        <v>45.04254564352068</v>
       </c>
       <c r="B15" t="n">
-        <v>49.14933248049705</v>
+        <v>46.488046923064</v>
       </c>
       <c r="C15" t="n">
-        <v>33.6654435340314</v>
+        <v>38.57593158251487</v>
       </c>
       <c r="D15" t="n">
-        <v>5.001719388201426</v>
+        <v>5.973220914643597</v>
       </c>
       <c r="E15" t="n">
-        <v>4.675907173977767</v>
+        <v>4.766952271310776</v>
       </c>
       <c r="F15" t="n">
-        <v>2.919936645214246</v>
+        <v>3.115991183510241</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09846549301460367</v>
+        <v>0.08096357027573664</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1164892808153044</v>
+        <v>-0.1205391414910475</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5525991723467835</v>
+        <v>-0.5541741455878502</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7612614074971281</v>
+        <v>-0.7631004480977066</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.003286817207891883</v>
+        <v>-0.03599371789417674</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5622763130010004</v>
+        <v>-0.2433407199026936</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.08022266855197364</v>
+        <v>-0.001050702586802982</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91.39499359494657</v>
+        <v>87.12476042427809</v>
       </c>
       <c r="B16" t="n">
-        <v>71.73928884580609</v>
+        <v>68.02072344572842</v>
       </c>
       <c r="C16" t="n">
-        <v>40.57779576888055</v>
+        <v>38.5864875470172</v>
       </c>
       <c r="D16" t="n">
-        <v>12.42699708273639</v>
+        <v>12.89636170839678</v>
       </c>
       <c r="E16" t="n">
-        <v>4.966247263764</v>
+        <v>4.17149649435368</v>
       </c>
       <c r="F16" t="n">
-        <v>7.447872833486772</v>
+        <v>6.933086230530872</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006731470167421139</v>
+        <v>0.007796112813491549</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9026424586585747</v>
+        <v>-0.8732182855041335</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9495971445559377</v>
+        <v>-0.9349981854542457</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9868199188951724</v>
+        <v>-0.981505768329245</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1779556650648076</v>
+        <v>-0.02854988655985592</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5577269751217034</v>
+        <v>-0.3213990043082586</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.02761625624047194</v>
+        <v>-0.00351376097067993</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>51.46519531656089</v>
+        <v>47.39982460532192</v>
       </c>
       <c r="B17" t="n">
-        <v>48.96195442866753</v>
+        <v>43.87769274417861</v>
       </c>
       <c r="C17" t="n">
-        <v>33.76670886362422</v>
+        <v>38.58088746956291</v>
       </c>
       <c r="D17" t="n">
-        <v>5.004083670914564</v>
+        <v>5.265544567064127</v>
       </c>
       <c r="E17" t="n">
-        <v>4.134941776153931</v>
+        <v>4.244345464263602</v>
       </c>
       <c r="F17" t="n">
-        <v>3.70515791551424</v>
+        <v>3.286802732300934</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04974690508365298</v>
+        <v>0.06652583609673086</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4830061770378457</v>
+        <v>-0.244464806017057</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7229303542625047</v>
+        <v>-0.609511875139354</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8825675099287545</v>
+        <v>-0.8063488823874574</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5193744105066815</v>
+        <v>-0.08571331333426391</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.614174457334945</v>
+        <v>-0.1514068403924451</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1003524077122311</v>
+        <v>-0.00220707623134489</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54.2274480566856</v>
+        <v>57.51579415508733</v>
       </c>
       <c r="B18" t="n">
-        <v>58.50817683203626</v>
+        <v>67.41702838917772</v>
       </c>
       <c r="C18" t="n">
-        <v>38.78116545301752</v>
+        <v>38.57476227046761</v>
       </c>
       <c r="D18" t="n">
-        <v>5.557267704485214</v>
+        <v>9.99746859441573</v>
       </c>
       <c r="E18" t="n">
-        <v>4.495970294005952</v>
+        <v>3.966207889843593</v>
       </c>
       <c r="F18" t="n">
-        <v>3.997132129891913</v>
+        <v>4.332576716198981</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04104732942797432</v>
+        <v>0.03327879071327951</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5568595371275153</v>
+        <v>-0.5711913402956074</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7603281693374361</v>
+        <v>-0.7670549124667916</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9041817851265608</v>
+        <v>-0.9079939077619007</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4408616441449366</v>
+        <v>-0.01203922977162031</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5280773838952039</v>
+        <v>-0.6142666963155532</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0003589570371936413</v>
+        <v>-0.0007778631091091837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>58.1744721870474</v>
+        <v>97.8340391047264</v>
       </c>
       <c r="B19" t="n">
-        <v>55.83030518007226</v>
+        <v>47.92752979331976</v>
       </c>
       <c r="C19" t="n">
-        <v>33.56041972491013</v>
+        <v>38.59336670588025</v>
       </c>
       <c r="D19" t="n">
-        <v>5.000302037046978</v>
+        <v>11.48333766726397</v>
       </c>
       <c r="E19" t="n">
-        <v>4.948672452915785</v>
+        <v>4.433133433778573</v>
       </c>
       <c r="F19" t="n">
-        <v>4.288837429220525</v>
+        <v>8.161713192749996</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03161805896663376</v>
+        <v>0.005202089151262518</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6399093832570514</v>
+        <v>-0.9087601353314055</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8042066648271249</v>
+        <v>-0.9529395283259932</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9271593805010933</v>
+        <v>-0.9879157913584039</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03723390920088107</v>
+        <v>-0.05475162562983459</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4553332710065469</v>
+        <v>-0.5720675286211756</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.06189710451215924</v>
+        <v>-0.005118898038724978</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>41.86773713899267</v>
+        <v>70.33664919370955</v>
       </c>
       <c r="B20" t="n">
-        <v>52.19925546057215</v>
+        <v>66.64795965006412</v>
       </c>
       <c r="C20" t="n">
-        <v>38.97272834988284</v>
+        <v>38.74396165991995</v>
       </c>
       <c r="D20" t="n">
-        <v>6.563943613473312</v>
+        <v>7.569304109252327</v>
       </c>
       <c r="E20" t="n">
-        <v>4.394040247505862</v>
+        <v>3.975400270503639</v>
       </c>
       <c r="F20" t="n">
-        <v>2.880144179870472</v>
+        <v>5.586452037764108</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1095956035133423</v>
+        <v>0.01576347285045357</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.04506665924241763</v>
+        <v>-0.763506814832705</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5214802933572315</v>
+        <v>-0.8735614114340209</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7350450881111813</v>
+        <v>-0.9581123397853833</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01223542911334681</v>
+        <v>-0.1508559227456188</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6787558176048639</v>
+        <v>-0.6954654448934938</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.03938345850348923</v>
+        <v>-0.04025772064798774</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>43.51010059070657</v>
+        <v>50.88358110847491</v>
       </c>
       <c r="B21" t="n">
-        <v>48.84562879818958</v>
+        <v>49.31024821047009</v>
       </c>
       <c r="C21" t="n">
-        <v>33.71548977831009</v>
+        <v>38.61208662829765</v>
       </c>
       <c r="D21" t="n">
-        <v>5.000282118319038</v>
+        <v>5.005075024808796</v>
       </c>
       <c r="E21" t="n">
-        <v>4.862754824403923</v>
+        <v>4.141591920943294</v>
       </c>
       <c r="F21" t="n">
-        <v>2.962748936420283</v>
+        <v>3.659014948463169</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09378332439475394</v>
+        <v>0.05084719097740668</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1494158463838278</v>
+        <v>-0.3871286100868662</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5670582136110742</v>
+        <v>-0.6759051045541161</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7729827380832197</v>
+        <v>-0.853086871116978</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.00778892758406693</v>
+        <v>-0.1325928140279962</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5725810645960134</v>
+        <v>-0.5238433265042225</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.09013118282918746</v>
+        <v>-0.009486879936117937</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>49.28406334290899</v>
+        <v>68.68020890126859</v>
       </c>
       <c r="B22" t="n">
-        <v>47.63311569993108</v>
+        <v>48.80930279966854</v>
       </c>
       <c r="C22" t="n">
-        <v>38.79476311428863</v>
+        <v>38.75261782305175</v>
       </c>
       <c r="D22" t="n">
-        <v>5.000387080099915</v>
+        <v>7.434617049664321</v>
       </c>
       <c r="E22" t="n">
-        <v>4.555309129038901</v>
+        <v>4.391927712545542</v>
       </c>
       <c r="F22" t="n">
-        <v>3.450938717887655</v>
+        <v>5.353189772049226</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05857353685048815</v>
+        <v>0.01717275057877185</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4121985852825277</v>
+        <v>-0.7463686394236115</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6881673999946444</v>
+        <v>-0.8635158201707058</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8608195923351765</v>
+        <v>-0.9540702495092173</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2496911140796041</v>
+        <v>-0.004145054778706303</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6945088992004721</v>
+        <v>-0.684974656374701</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.00312902347957761</v>
+        <v>-0.04227749204540748</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>52.5632318164831</v>
+        <v>49.38661667259283</v>
       </c>
       <c r="B23" t="n">
-        <v>55.32959242420993</v>
+        <v>41.52830350956371</v>
       </c>
       <c r="C23" t="n">
-        <v>38.77981064116293</v>
+        <v>38.5771498183013</v>
       </c>
       <c r="D23" t="n">
-        <v>5.000020324195716</v>
+        <v>5.013795429614387</v>
       </c>
       <c r="E23" t="n">
-        <v>4.565726714034971</v>
+        <v>2.009091272953137</v>
       </c>
       <c r="F23" t="n">
-        <v>3.841225650081041</v>
+        <v>3.482690341131106</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04595736120770656</v>
+        <v>0.05690585815232092</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5143329405807973</v>
+        <v>-0.3312504882161524</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7386609716973992</v>
+        <v>-0.649601429593909</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8918873273860276</v>
+        <v>-0.8352695165461691</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7459099188110653</v>
+        <v>-0.2944387912812709</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5686055172213974</v>
+        <v>-0.0739219497688796</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.295965945941952e-05</v>
+        <v>-0.00133495760363575</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67.7715041087156</v>
+        <v>60.72634097141363</v>
       </c>
       <c r="B24" t="n">
-        <v>53.70772523770757</v>
+        <v>53.83541982436028</v>
       </c>
       <c r="C24" t="n">
-        <v>38.78142774010977</v>
+        <v>38.58173149330263</v>
       </c>
       <c r="D24" t="n">
-        <v>6.791966492956371</v>
+        <v>8.775455893239117</v>
       </c>
       <c r="E24" t="n">
-        <v>4.894355671990292</v>
+        <v>4.076842759441427</v>
       </c>
       <c r="F24" t="n">
-        <v>5.125873709959938</v>
+        <v>4.542067210041243</v>
       </c>
       <c r="G24" t="n">
-        <v>0.018349326317455</v>
+        <v>0.02706474133005774</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7696893143374589</v>
+        <v>-0.6363408417311439</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8773287669063747</v>
+        <v>-0.802088476019759</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9595139573454403</v>
+        <v>-0.9262486941606464</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.007317604637143544</v>
+        <v>-0.04170262826370649</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7000069879067069</v>
+        <v>-0.2829923980363216</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0004123892163032124</v>
+        <v>-0.002404015103947138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87.07365437869029</v>
+        <v>48.87166878931279</v>
       </c>
       <c r="B25" t="n">
-        <v>71.67851327231791</v>
+        <v>44.09838082216987</v>
       </c>
       <c r="C25" t="n">
-        <v>40.58910646413095</v>
+        <v>38.6052540855157</v>
       </c>
       <c r="D25" t="n">
-        <v>12.40824492357252</v>
+        <v>5.017892622318808</v>
       </c>
       <c r="E25" t="n">
-        <v>4.971190793651163</v>
+        <v>4.704645613208745</v>
       </c>
       <c r="F25" t="n">
-        <v>6.959392094127862</v>
+        <v>3.424023208079821</v>
       </c>
       <c r="G25" t="n">
-        <v>0.007956956253814622</v>
+        <v>0.05920602138189286</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8880087234781623</v>
+        <v>-0.3101132369154522</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.941921703339973</v>
+        <v>-0.6397274055093357</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9841717231108577</v>
+        <v>-0.8283362577184524</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0929325019758413</v>
+        <v>-0.03201133791830632</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5185560057866149</v>
+        <v>-0.1428765860061137</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.02522678144870602</v>
+        <v>-0.007892619953662056</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>76.81955547370526</v>
+        <v>58.33620889296003</v>
       </c>
       <c r="B26" t="n">
-        <v>49.14493478862992</v>
+        <v>67.9090228193219</v>
       </c>
       <c r="C26" t="n">
-        <v>33.63972402473067</v>
+        <v>38.57359653813843</v>
       </c>
       <c r="D26" t="n">
-        <v>5.001998140241898</v>
+        <v>9.973820580078252</v>
       </c>
       <c r="E26" t="n">
-        <v>4.441216937309076</v>
+        <v>4.227565967044435</v>
       </c>
       <c r="F26" t="n">
-        <v>6.128543467144495</v>
+        <v>4.419246005276837</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01165971964826137</v>
+        <v>0.03156244820958874</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8405247992980858</v>
+        <v>-0.5888033621344119</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9190404229414845</v>
+        <v>-0.7762895644872342</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.975043059132868</v>
+        <v>-0.9129604395946717</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5766925287200309</v>
+        <v>-0.03939758449079206</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5990770030352981</v>
+        <v>-0.6194626563220802</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07573488127110134</v>
+        <v>-0.0005058588989684254</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>62.82958000566246</v>
+        <v>55.2029343125031</v>
       </c>
       <c r="B27" t="n">
-        <v>49.15175923320541</v>
+        <v>52.89992239742097</v>
       </c>
       <c r="C27" t="n">
-        <v>39.13661557774466</v>
+        <v>38.76996059694842</v>
       </c>
       <c r="D27" t="n">
-        <v>5.001737839192367</v>
+        <v>5.701136259965784</v>
       </c>
       <c r="E27" t="n">
-        <v>4.426716995075261</v>
+        <v>4.441404532782936</v>
       </c>
       <c r="F27" t="n">
-        <v>4.911881562442204</v>
+        <v>4.286344490899678</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02382207319926895</v>
+        <v>0.03754593949960388</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7129933530598566</v>
+        <v>-0.5184438288937051</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8446746477959686</v>
+        <v>-0.7405487833387672</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9460007492185185</v>
+        <v>-0.8932001687649783</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7521190109194946</v>
+        <v>-0.8152654046760504</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.3383977104419709</v>
+        <v>-0.334871623827989</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.06464789430485939</v>
+        <v>-0.04632413928796458</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>44.74725058390348</v>
+        <v>47.0461078111659</v>
       </c>
       <c r="B28" t="n">
-        <v>47.60907542757328</v>
+        <v>43.89420453664015</v>
       </c>
       <c r="C28" t="n">
-        <v>33.43503107665555</v>
+        <v>38.58088746956291</v>
       </c>
       <c r="D28" t="n">
-        <v>5.000353852975498</v>
+        <v>5.265544567064127</v>
       </c>
       <c r="E28" t="n">
-        <v>4.553266987905227</v>
+        <v>4.244345464263602</v>
       </c>
       <c r="F28" t="n">
-        <v>3.071040177729161</v>
+        <v>3.247445905174129</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08431811376435205</v>
+        <v>0.06844422024709187</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.217343256808634</v>
+        <v>-0.2274615259842517</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.597342237364987</v>
+        <v>-0.6017967481644405</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.7966823094967471</v>
+        <v>-0.8005512037613955</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.02938677243254823</v>
+        <v>-0.03683383433555887</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5915927517775887</v>
+        <v>-0.1652017953645302</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.04146583307149225</v>
+        <v>-0.00220707623134489</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>45.12874289480762</v>
+        <v>76.50182121726695</v>
       </c>
       <c r="B29" t="n">
-        <v>47.54314091081416</v>
+        <v>56.48776684240755</v>
       </c>
       <c r="C29" t="n">
-        <v>38.78001656144294</v>
+        <v>38.59455066702166</v>
       </c>
       <c r="D29" t="n">
-        <v>5.000019199666664</v>
+        <v>5.586371415900562</v>
       </c>
       <c r="E29" t="n">
-        <v>4.553266987905227</v>
+        <v>4.122256521441852</v>
       </c>
       <c r="F29" t="n">
-        <v>3.083510900696075</v>
+        <v>6.195029311278893</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08168186884589106</v>
+        <v>0.01162000781001123</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2367670073852947</v>
+        <v>-0.8153177131905111</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6061127904807007</v>
+        <v>-0.9049111182788577</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8033285518675477</v>
+        <v>-0.9697689363505443</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.06580371129584682</v>
+        <v>-0.2028530474791859</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6230822193335845</v>
+        <v>-0.4299150098608751</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0001249089951642089</v>
+        <v>-0.005395155638389382</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>55.91732089677188</v>
+        <v>60.0208501839013</v>
       </c>
       <c r="B30" t="n">
-        <v>56.7216902678972</v>
+        <v>53.83541982436028</v>
       </c>
       <c r="C30" t="n">
-        <v>38.79476311428863</v>
+        <v>38.58167244742356</v>
       </c>
       <c r="D30" t="n">
-        <v>5.000387080099915</v>
+        <v>8.775455893239117</v>
       </c>
       <c r="E30" t="n">
-        <v>4.258017612044224</v>
+        <v>4.174326408747138</v>
       </c>
       <c r="F30" t="n">
-        <v>4.112815487505186</v>
+        <v>4.461779635121797</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03656285161829221</v>
+        <v>0.02826168686025224</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5953738899034751</v>
+        <v>-0.6235655468765136</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7804507148576205</v>
+        <v>-0.7952088818147686</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9150460753171124</v>
+        <v>-0.9228060562542131</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.397050174592547</v>
+        <v>-0.004224440612345031</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4823358404677525</v>
+        <v>-0.31165296127901</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.00312902347957761</v>
+        <v>-0.002390237732165928</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96.85906528647288</v>
+        <v>62.21962171634987</v>
       </c>
       <c r="B31" t="n">
-        <v>66.26348437724756</v>
+        <v>54.00439990266294</v>
       </c>
       <c r="C31" t="n">
-        <v>38.77998677596433</v>
+        <v>38.5754048059224</v>
       </c>
       <c r="D31" t="n">
-        <v>11.59183038110565</v>
+        <v>8.775455893239117</v>
       </c>
       <c r="E31" t="n">
-        <v>4.383618344547727</v>
+        <v>2.104702268816882</v>
       </c>
       <c r="F31" t="n">
-        <v>7.997416079565355</v>
+        <v>4.714924497448105</v>
       </c>
       <c r="G31" t="n">
-        <v>0.005486081314148413</v>
+        <v>0.02474214347538711</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9177434547555231</v>
+        <v>-0.6615142349811824</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9578371177969118</v>
+        <v>-0.8158004443912826</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9894327849862863</v>
+        <v>-0.9329162099354423</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1975806829754716</v>
+        <v>-0.03824113121402397</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5985439716667982</v>
+        <v>-0.2871399737278178</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0001188412050405494</v>
+        <v>-0.0009277880485605849</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46.86523709321058</v>
+        <v>72.96060392506595</v>
       </c>
       <c r="B32" t="n">
-        <v>47.54314091081416</v>
+        <v>70.23126166880887</v>
       </c>
       <c r="C32" t="n">
-        <v>38.78001656144294</v>
+        <v>38.59267615538526</v>
       </c>
       <c r="D32" t="n">
-        <v>5.180506447576111</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="E32" t="n">
-        <v>4.601740104979082</v>
+        <v>4.001930687397234</v>
       </c>
       <c r="F32" t="n">
-        <v>3.216531187093518</v>
+        <v>5.796043182871164</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0708977574216421</v>
+        <v>0.01377744479900244</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3175086933536621</v>
+        <v>-0.787742027843028</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6432029168460774</v>
+        <v>-0.8880679359201251</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8303687867675945</v>
+        <v>-0.9636874230145837</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02923909536293655</v>
+        <v>-0.05910250826267435</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.7112326640885158</v>
+        <v>-0.5951718168302556</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0001249089951642089</v>
+        <v>-0.00495776958989419</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>54.2274480566856</v>
+        <v>43.41755894001421</v>
       </c>
       <c r="B33" t="n">
-        <v>50.90596529282303</v>
+        <v>49.1658478431422</v>
       </c>
       <c r="C33" t="n">
-        <v>38.78116545301752</v>
+        <v>38.5761875136873</v>
       </c>
       <c r="D33" t="n">
-        <v>5.0610437043794</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="E33" t="n">
-        <v>4.604461631455827</v>
+        <v>4.387858457787964</v>
       </c>
       <c r="F33" t="n">
-        <v>4.056532151361082</v>
+        <v>2.9994784555182</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04090201675809441</v>
+        <v>0.09331465796090009</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5571147896096911</v>
+        <v>-0.01878259825918126</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7605278074228381</v>
+        <v>-0.5102111798216851</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9042971126423386</v>
+        <v>-0.7260323047473008</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.9737951980875739</v>
+        <v>-0.01055078333003848</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.499539898554665</v>
+        <v>-0.3067152013394461</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0003589570371936413</v>
+        <v>-0.001110419860370498</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>75.6315023496564</v>
+        <v>77.44246289629278</v>
       </c>
       <c r="B34" t="n">
-        <v>42.02073254899009</v>
+        <v>49.4537326420368</v>
       </c>
       <c r="C34" t="n">
-        <v>38.79476311428863</v>
+        <v>38.57589003733644</v>
       </c>
       <c r="D34" t="n">
-        <v>5.000387080099915</v>
+        <v>5.581933982819951</v>
       </c>
       <c r="E34" t="n">
-        <v>4.608509419155181</v>
+        <v>2.578333020360433</v>
       </c>
       <c r="F34" t="n">
-        <v>5.961962436723448</v>
+        <v>6.330638554437778</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01232039942104665</v>
+        <v>0.01112998842559659</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8331066643458782</v>
+        <v>-0.8217984493062934</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9150921917291742</v>
+        <v>-0.9089229040913213</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9735085256466071</v>
+        <v>-0.9711548881433968</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.442591639539095</v>
+        <v>-0.3184311835993964</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6432455394415507</v>
+        <v>-0.3860183981730037</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.00312902347957761</v>
+        <v>-0.001041008711834962</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>45.78320129630541</v>
+        <v>45.71142424879198</v>
       </c>
       <c r="B35" t="n">
-        <v>47.527120154429</v>
+        <v>46.36492657585814</v>
       </c>
       <c r="C35" t="n">
-        <v>38.78001656144294</v>
+        <v>39.09723898411775</v>
       </c>
       <c r="D35" t="n">
-        <v>5.32038993367731</v>
+        <v>5.667243032653428</v>
       </c>
       <c r="E35" t="n">
-        <v>4.642113210081789</v>
+        <v>4.336388964061059</v>
       </c>
       <c r="F35" t="n">
-        <v>3.130697352603526</v>
+        <v>3.159631309408006</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0774952636799172</v>
+        <v>0.07648002897778296</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.268470925108126</v>
+        <v>-0.158327131099332</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.620523402819263</v>
+        <v>-0.5708281162739047</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.814029872082033</v>
+        <v>-0.7765189716172681</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.00328735635127274</v>
+        <v>-0.02216666007390641</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.6915763733247251</v>
+        <v>-0.2172544542971132</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0001249089951642089</v>
+        <v>-0.122689096294141</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>46.59105049526729</v>
+        <v>43.94355968767051</v>
       </c>
       <c r="B36" t="n">
-        <v>47.54314091081416</v>
+        <v>48.19061186612254</v>
       </c>
       <c r="C36" t="n">
-        <v>38.78001656144294</v>
+        <v>38.5784053255879</v>
       </c>
       <c r="D36" t="n">
-        <v>5.32038993367731</v>
+        <v>6.220955004617943</v>
       </c>
       <c r="E36" t="n">
-        <v>4.553266987905227</v>
+        <v>4.331754203729267</v>
       </c>
       <c r="F36" t="n">
-        <v>3.203450181524942</v>
+        <v>3.030931457409482</v>
       </c>
       <c r="G36" t="n">
-        <v>0.07252972319657171</v>
+        <v>0.08905269263132015</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3054654060866412</v>
+        <v>-0.05339092334942659</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.637588061936128</v>
+        <v>-0.5250287733614456</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8263813750739357</v>
+        <v>-0.7387936164754288</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04319468952898649</v>
+        <v>-0.002382922160819665</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.7103868760061353</v>
+        <v>-0.2862011721808499</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0001249089951642089</v>
+        <v>-0.001627909303843628</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48.34851579199123</v>
+        <v>71.38549268160631</v>
       </c>
       <c r="B37" t="n">
-        <v>51.14935502305028</v>
+        <v>69.91045985613998</v>
       </c>
       <c r="C37" t="n">
-        <v>38.78116545301752</v>
+        <v>38.61859150670636</v>
       </c>
       <c r="D37" t="n">
-        <v>5.007484426694635</v>
+        <v>7.526374953834749</v>
       </c>
       <c r="E37" t="n">
-        <v>4.554919907972403</v>
+        <v>4.00441539030795</v>
       </c>
       <c r="F37" t="n">
-        <v>3.344773260369138</v>
+        <v>5.718334523753396</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06297961857808158</v>
+        <v>0.01494333098724844</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3778147411893967</v>
+        <v>-0.7735736998326346</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6716520535269902</v>
+        <v>-0.8795337673350894</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8499372581765574</v>
+        <v>-0.9604456919093942</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1099333695794789</v>
+        <v>-0.2102341520070993</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.7159515490643388</v>
+        <v>-0.6686770081917058</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0003589570371936413</v>
+        <v>-0.0110046848981496</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>85.63930910525013</v>
+        <v>54.23059872334339</v>
       </c>
       <c r="B38" t="n">
-        <v>71.06539336727982</v>
+        <v>49.31024821047009</v>
       </c>
       <c r="C38" t="n">
-        <v>38.88763409338315</v>
+        <v>38.6119914908332</v>
       </c>
       <c r="D38" t="n">
-        <v>12.65321681898344</v>
+        <v>5.005075024808796</v>
       </c>
       <c r="E38" t="n">
-        <v>4.35773628529883</v>
+        <v>4.376647268756702</v>
       </c>
       <c r="F38" t="n">
-        <v>6.799998834817205</v>
+        <v>4.073490456711939</v>
       </c>
       <c r="G38" t="n">
-        <v>0.008410676365888357</v>
+        <v>0.0400463589744332</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8825393973287752</v>
+        <v>-0.4925848608810017</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9391400201664856</v>
+        <v>-0.7275494421583315</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9831581001583741</v>
+        <v>-0.8855772252235786</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.08901789561933716</v>
+        <v>-0.6184637305398863</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5059211225146737</v>
+        <v>-0.3774113058537267</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.02204836391113555</v>
+        <v>-0.009464681194412405</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>48.58764371958379</v>
+        <v>68.78600772103115</v>
       </c>
       <c r="B39" t="n">
-        <v>49.2137660101824</v>
+        <v>49.09403517339822</v>
       </c>
       <c r="C39" t="n">
-        <v>33.64063758685032</v>
+        <v>38.78196001933821</v>
       </c>
       <c r="D39" t="n">
-        <v>5.002001064196033</v>
+        <v>7.566812882535884</v>
       </c>
       <c r="E39" t="n">
-        <v>4.550340007065007</v>
+        <v>4.313436103664738</v>
       </c>
       <c r="F39" t="n">
-        <v>3.368378211052034</v>
+        <v>5.383733574915116</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06180884947912494</v>
+        <v>0.0170845978705146</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.3868630802088753</v>
+        <v>-0.7474939435214057</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6759780520506453</v>
+        <v>-0.864164719356189</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8528221282318087</v>
+        <v>-0.9543358216678588</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.01400962892928615</v>
+        <v>-0.04646342929586145</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.7114489774062422</v>
+        <v>-0.6856447155665306</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.07589428837381648</v>
+        <v>-0.0491240045122486</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>52.51585873311168</v>
+        <v>45.62834350056963</v>
       </c>
       <c r="B40" t="n">
-        <v>59.17925225339265</v>
+        <v>46.37968049007215</v>
       </c>
       <c r="C40" t="n">
-        <v>38.77981064116293</v>
+        <v>38.6966053509382</v>
       </c>
       <c r="D40" t="n">
-        <v>5.000020324195716</v>
+        <v>5.708704569620211</v>
       </c>
       <c r="E40" t="n">
-        <v>4.565726714034971</v>
+        <v>4.140868866470994</v>
       </c>
       <c r="F40" t="n">
-        <v>3.812645407522814</v>
+        <v>3.148593116223063</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04613180113622238</v>
+        <v>0.07700756559498943</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5130024143583539</v>
+        <v>-0.1537672742400813</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7379795805201824</v>
+        <v>-0.5688110129629501</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8914900404167199</v>
+        <v>-0.7749131520737408</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.6012005977444308</v>
+        <v>-0.01664168752972914</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5739653762564951</v>
+        <v>-0.2204946034777846</v>
       </c>
       <c r="M40" t="n">
-        <v>-8.295965945941952e-05</v>
+        <v>-0.02920791521891383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>44.22154508280934</v>
+        <v>62.07613338735023</v>
       </c>
       <c r="B41" t="n">
-        <v>48.62247125260284</v>
+        <v>54.00439990266294</v>
       </c>
       <c r="C41" t="n">
-        <v>38.78278959083624</v>
+        <v>38.57591495081201</v>
       </c>
       <c r="D41" t="n">
-        <v>5.17235596693784</v>
+        <v>8.775455893239117</v>
       </c>
       <c r="E41" t="n">
-        <v>4.600852077648544</v>
+        <v>2.104702268816882</v>
       </c>
       <c r="F41" t="n">
-        <v>3.006145174233483</v>
+        <v>4.698129516964899</v>
       </c>
       <c r="G41" t="n">
-        <v>0.08831422183091558</v>
+        <v>0.0249536694051209</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.1892187079548921</v>
+        <v>-0.6591994962347747</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5846935042239103</v>
+        <v>-0.8145306921050975</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7869081959469307</v>
+        <v>-0.9323096965865697</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.006767771261934785</v>
+        <v>-0.03082098531673722</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6256335763078447</v>
+        <v>-0.2928197200840538</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.0006898205275937531</v>
+        <v>-0.001046821856135749</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>45.98686248280861</v>
+        <v>65.08664895299142</v>
       </c>
       <c r="B42" t="n">
-        <v>47.62094931507971</v>
+        <v>73.60342011811456</v>
       </c>
       <c r="C42" t="n">
-        <v>38.7810721627917</v>
+        <v>38.59354486981913</v>
       </c>
       <c r="D42" t="n">
-        <v>5.261805057080388</v>
+        <v>8.386954563410958</v>
       </c>
       <c r="E42" t="n">
-        <v>4.968556061595478</v>
+        <v>4.543113909065607</v>
       </c>
       <c r="F42" t="n">
-        <v>3.145691568770301</v>
+        <v>5.01219144532128</v>
       </c>
       <c r="G42" t="n">
-        <v>0.07618177099437244</v>
+        <v>0.02094201073301159</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.27807330094553</v>
+        <v>-0.7027316114163272</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6249375399507715</v>
+        <v>-0.8384461759896017</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8172626031376409</v>
+        <v>-0.943349496102756</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.008330703903267598</v>
+        <v>-0.01558868135319092</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6922432290242366</v>
+        <v>-0.6622154433689458</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.0003399522893335422</v>
+        <v>-0.005160469624464759</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>90.24301643764515</v>
+        <v>95.84244594203261</v>
       </c>
       <c r="B43" t="n">
-        <v>73.30837395730161</v>
+        <v>64.46745503228851</v>
       </c>
       <c r="C43" t="n">
-        <v>38.77998683182212</v>
+        <v>38.7536511647413</v>
       </c>
       <c r="D43" t="n">
-        <v>11.79441864566541</v>
+        <v>11.97038341359188</v>
       </c>
       <c r="E43" t="n">
-        <v>4.33240205046487</v>
+        <v>4.429461347340398</v>
       </c>
       <c r="F43" t="n">
-        <v>7.153556109137483</v>
+        <v>7.954313938861201</v>
       </c>
       <c r="G43" t="n">
-        <v>0.007000750944186502</v>
+        <v>0.005588688764017461</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.8990996714687008</v>
+        <v>-0.903137294589107</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.9477871113306996</v>
+        <v>-0.9498951276477888</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.9861982767681917</v>
+        <v>-0.9869295882124994</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.007744511729042931</v>
+        <v>-0.07300015327432754</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5491216254293634</v>
+        <v>-0.5578774273369824</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0001188525841877897</v>
+        <v>-0.04251860510630229</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56.85382040475599</v>
+        <v>50.03619827557783</v>
       </c>
       <c r="B44" t="n">
-        <v>56.11011267863791</v>
+        <v>49.29511269128655</v>
       </c>
       <c r="C44" t="n">
-        <v>38.8323463449069</v>
+        <v>38.59415891505551</v>
       </c>
       <c r="D44" t="n">
-        <v>5.000387080099915</v>
+        <v>5.010860866864829</v>
       </c>
       <c r="E44" t="n">
-        <v>4.258017612044224</v>
+        <v>4.239455103404638</v>
       </c>
       <c r="F44" t="n">
-        <v>4.178675394345129</v>
+        <v>3.558687541173247</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03440196527672858</v>
+        <v>0.05416804279570599</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6146963668207845</v>
+        <v>-0.3558169010373978</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7906793587342319</v>
+        <v>-0.6609940901638746</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9203565089476321</v>
+        <v>-0.8430643700172804</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.270734369898155</v>
+        <v>-0.01140271744906145</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.4732807958807274</v>
+        <v>-0.56091632544347</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0107853434787573</v>
+        <v>-0.005303746846286456</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>73.34585731518575</v>
+        <v>50.2033653886691</v>
       </c>
       <c r="B45" t="n">
-        <v>34.19465713337304</v>
+        <v>49.09669801233432</v>
       </c>
       <c r="C45" t="n">
-        <v>38.78278959083624</v>
+        <v>38.61495803386475</v>
       </c>
       <c r="D45" t="n">
-        <v>5.147172110741005</v>
+        <v>5.08791249717512</v>
       </c>
       <c r="E45" t="n">
-        <v>4.974627379349094</v>
+        <v>4.507049357157912</v>
       </c>
       <c r="F45" t="n">
-        <v>5.661120280202402</v>
+        <v>3.588129268098061</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0137438432896555</v>
+        <v>0.05350370033483113</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8174476175796231</v>
+        <v>-0.3621363520012111</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9062125532936905</v>
+        <v>-0.6639838743248944</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9701960595761742</v>
+        <v>-0.8450954017658983</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1244637823919678</v>
+        <v>-0.06508011211966276</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.7045826241106296</v>
+        <v>-0.553602764245727</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0006898205275937531</v>
+        <v>-0.01015687456844022</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>94.26547592526073</v>
+        <v>74.81537081940712</v>
       </c>
       <c r="B46" t="n">
-        <v>63.42584873198503</v>
+        <v>49.09403517339822</v>
       </c>
       <c r="C46" t="n">
-        <v>38.78003722916169</v>
+        <v>38.61163126879261</v>
       </c>
       <c r="D46" t="n">
-        <v>11.66979957750609</v>
+        <v>6.076192106020666</v>
       </c>
       <c r="E46" t="n">
-        <v>4.945968579502573</v>
+        <v>2.543141616845002</v>
       </c>
       <c r="F46" t="n">
-        <v>7.659115286551271</v>
+        <v>6.014395215286951</v>
       </c>
       <c r="G46" t="n">
-        <v>0.006020599776420571</v>
+        <v>0.01258909068970627</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.9110502629277207</v>
+        <v>-0.8028245755172868</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9541869030178421</v>
+        <v>-0.8972254451962269</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.988296032615663</v>
+        <v>-0.9670468113602029</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1213212493052782</v>
+        <v>-0.1491048106523576</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.579169678287712</v>
+        <v>-0.5086160284276674</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0001291193481795599</v>
+        <v>-0.009380629384942857</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>43.22533905456722</v>
+        <v>74.2701929266627</v>
       </c>
       <c r="B47" t="n">
-        <v>49.14933248049705</v>
+        <v>48.82848169597025</v>
       </c>
       <c r="C47" t="n">
-        <v>33.6654435340314</v>
+        <v>38.59267615538526</v>
       </c>
       <c r="D47" t="n">
-        <v>5.166723844140375</v>
+        <v>6.407980481947774</v>
       </c>
       <c r="E47" t="n">
-        <v>4.675907173977767</v>
+        <v>4.001930687397234</v>
       </c>
       <c r="F47" t="n">
-        <v>2.953773020350981</v>
+        <v>5.977764053590857</v>
       </c>
       <c r="G47" t="n">
-        <v>0.09622520184655702</v>
+        <v>0.01293133789295798</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1325689883604698</v>
+        <v>-0.7985230823334856</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.5596265598098437</v>
+        <v>-0.8945920246859081</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.7669839834244999</v>
+        <v>-0.966093957517877</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02768023852186045</v>
+        <v>-0.1829183743554969</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5751057061648345</v>
+        <v>-0.5340576634224072</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.08022266855197364</v>
+        <v>-0.00495776958989419</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>72.63584718032122</v>
+        <v>43.93160072503701</v>
       </c>
       <c r="B48" t="n">
-        <v>49.12328201113426</v>
+        <v>48.19061186612254</v>
       </c>
       <c r="C48" t="n">
-        <v>38.90116962940114</v>
+        <v>38.5784053255879</v>
       </c>
       <c r="D48" t="n">
-        <v>5.562592282920054</v>
+        <v>6.222338570045137</v>
       </c>
       <c r="E48" t="n">
-        <v>4.345345514833642</v>
+        <v>2.68688498354215</v>
       </c>
       <c r="F48" t="n">
-        <v>5.616920762151119</v>
+        <v>3.029861533615703</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01424600927118703</v>
+        <v>0.08914589968290995</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8121419842372004</v>
+        <v>-0.05262343732239801</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9029858444969352</v>
+        <v>-0.5246988479611858</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9690477781878071</v>
+        <v>-0.7385125020683261</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.1598356218090966</v>
+        <v>-0.001642239490803376</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.7148658590917631</v>
+        <v>-0.2866675717235564</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.02480577442133727</v>
+        <v>-0.001627909303843628</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>44.23280967195069</v>
+        <v>53.48867092939076</v>
       </c>
       <c r="B49" t="n">
-        <v>48.62247125260284</v>
+        <v>49.36483006726686</v>
       </c>
       <c r="C49" t="n">
-        <v>38.78278959083624</v>
+        <v>38.59367184138724</v>
       </c>
       <c r="D49" t="n">
-        <v>5.17235596693784</v>
+        <v>5.000079389119043</v>
       </c>
       <c r="E49" t="n">
-        <v>4.600852077648544</v>
+        <v>4.6214052940079</v>
       </c>
       <c r="F49" t="n">
-        <v>3.007355254268873</v>
+        <v>3.978440871909529</v>
       </c>
       <c r="G49" t="n">
-        <v>0.08822831232869272</v>
+        <v>0.04216079741970501</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1898323091487121</v>
+        <v>-0.4714531908946786</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5849677170175085</v>
+        <v>-0.7170120898810196</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7871219925343739</v>
+        <v>-0.8792302946158738</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.008260807324383841</v>
+        <v>-0.5095579433735231</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6256018963504109</v>
+        <v>-0.4098706468391539</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0006898205275937531</v>
+        <v>-0.005190096323689081</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58.83207637268816</v>
+        <v>55.16194969043495</v>
       </c>
       <c r="B50" t="n">
-        <v>53.12947550315091</v>
+        <v>49.86101462257145</v>
       </c>
       <c r="C50" t="n">
-        <v>33.80307793034731</v>
+        <v>21.36557736094865</v>
       </c>
       <c r="D50" t="n">
-        <v>5.004083670914564</v>
+        <v>5.010885585088158</v>
       </c>
       <c r="E50" t="n">
-        <v>4.115003788964722</v>
+        <v>3.823591104100514</v>
       </c>
       <c r="F50" t="n">
-        <v>4.456596545103015</v>
+        <v>4.162888741977024</v>
       </c>
       <c r="G50" t="n">
-        <v>0.03029304090532462</v>
+        <v>0.03755895600820174</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6517278039667734</v>
+        <v>-0.517586751335399</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8106446474964571</v>
+        <v>-0.7401631527379466</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9303102481343749</v>
+        <v>-0.8929848391568537</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.5716456389754307</v>
+        <v>-0.5580945048659811</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.4043481473265759</v>
+        <v>-0.3366647010434707</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1075073939962427</v>
+        <v>-0.2070350605706141</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>93.77057348439558</v>
+        <v>54.6424386899119</v>
       </c>
       <c r="B51" t="n">
-        <v>71.81695511052241</v>
+        <v>54.99402390152946</v>
       </c>
       <c r="C51" t="n">
-        <v>38.78739306644581</v>
+        <v>21.83176801693983</v>
       </c>
       <c r="D51" t="n">
-        <v>11.58682618622373</v>
+        <v>5.027605584045677</v>
       </c>
       <c r="E51" t="n">
-        <v>4.955116880309894</v>
+        <v>3.828286586604401</v>
       </c>
       <c r="F51" t="n">
-        <v>7.583960983732025</v>
+        <v>4.110270368349242</v>
       </c>
       <c r="G51" t="n">
-        <v>0.006128476413740788</v>
+        <v>0.03891863858350758</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9096950184550763</v>
+        <v>-0.5038553578539399</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9534588247251699</v>
+        <v>-0.733218344122749</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9880630444997912</v>
+        <v>-0.888932592114587</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.0920535228449923</v>
+        <v>-0.4381785673233625</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5754727225449316</v>
+        <v>-0.3593933073163545</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.001627623952032397</v>
+        <v>-0.308749385514144</v>
       </c>
     </row>
   </sheetData>
